--- a/research/traditional_assets/database/data/norway/norway_education.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_education.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07835024335450255</v>
+        <v>0.07821297281912265</v>
       </c>
       <c r="C2">
-        <v>105.0996793896724</v>
+        <v>104.3749055545396</v>
       </c>
       <c r="D2">
-        <v>98.98967938967238</v>
+        <v>99.40890555453956</v>
       </c>
       <c r="E2">
-        <v>-40.6</v>
+        <v>-39.456</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.144</v>
       </c>
       <c r="G2">
         <v>6.11</v>
@@ -1439,28 +1439,28 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0575432</v>
       </c>
       <c r="N2">
-        <v>1.316666666666667</v>
+        <v>1.259123466666667</v>
       </c>
       <c r="O2">
-        <v>0.2896666666666668</v>
+        <v>0.2770071626666668</v>
       </c>
       <c r="P2">
-        <v>1.027000000000001</v>
+        <v>0.9821163040000005</v>
       </c>
       <c r="Q2">
-        <v>5.627000000000001</v>
+        <v>5.582116304</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07835024335450255</v>
+        <v>0.07860669981729561</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7576605038636399</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>22.88135985949108</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07821297281912265</v>
+        <v>0.07809910228374274</v>
       </c>
       <c r="C3">
-        <v>104.3749055545396</v>
+        <v>103.5813718058175</v>
       </c>
       <c r="D3">
-        <v>99.40890555453956</v>
+        <v>99.75937180581751</v>
       </c>
       <c r="E3">
-        <v>-39.456</v>
+        <v>-38.312</v>
       </c>
       <c r="F3">
-        <v>1.144</v>
+        <v>2.288</v>
       </c>
       <c r="G3">
         <v>6.11</v>
@@ -1521,45 +1521,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0575432</v>
+        <v>0.1185184</v>
       </c>
       <c r="N3">
-        <v>1.259123466666667</v>
+        <v>1.198148266666667</v>
       </c>
       <c r="O3">
-        <v>0.2770071626666668</v>
+        <v>0.2635926186666668</v>
       </c>
       <c r="P3">
-        <v>0.9821163040000005</v>
+        <v>0.9345556480000006</v>
       </c>
       <c r="Q3">
-        <v>5.582116304</v>
+        <v>5.534555648</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07860669981729561</v>
+        <v>0.07886839008545178</v>
       </c>
       <c r="T3">
-        <v>0.7576605038636399</v>
+        <v>0.7637041590173622</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>22.88135985949108</v>
+        <v>11.10938610938612</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07809910228374274</v>
+        <v>0.07803203174836283</v>
       </c>
       <c r="C4">
-        <v>103.5813718058175</v>
+        <v>102.6449576796593</v>
       </c>
       <c r="D4">
-        <v>99.75937180581751</v>
+        <v>99.96695767965927</v>
       </c>
       <c r="E4">
-        <v>-38.312</v>
+        <v>-37.168</v>
       </c>
       <c r="F4">
-        <v>2.288</v>
+        <v>3.432</v>
       </c>
       <c r="G4">
         <v>6.11</v>
@@ -1603,45 +1603,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M4">
-        <v>0.1185184</v>
+        <v>0.1863576</v>
       </c>
       <c r="N4">
-        <v>1.198148266666667</v>
+        <v>1.130309066666667</v>
       </c>
       <c r="O4">
-        <v>0.2635926186666668</v>
+        <v>0.2486679946666668</v>
       </c>
       <c r="P4">
-        <v>0.9345556480000006</v>
+        <v>0.8816410720000005</v>
       </c>
       <c r="Q4">
-        <v>5.534555648</v>
+        <v>5.481641072</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07886839008545178</v>
+        <v>0.07913547602924004</v>
       </c>
       <c r="T4">
-        <v>0.7637041590173622</v>
+        <v>0.769872425617553</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040404</v>
+        <v>0.042354</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>11.10938610938612</v>
+        <v>7.065269496208725</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07803203174836283</v>
+        <v>0.07795716121298293</v>
       </c>
       <c r="C5">
-        <v>102.6449576796593</v>
+        <v>101.7337076911483</v>
       </c>
       <c r="D5">
-        <v>99.96695767965927</v>
+        <v>100.1997076911483</v>
       </c>
       <c r="E5">
-        <v>-37.168</v>
+        <v>-36.024</v>
       </c>
       <c r="F5">
-        <v>3.432</v>
+        <v>4.576000000000001</v>
       </c>
       <c r="G5">
         <v>6.11</v>
@@ -1685,45 +1685,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M5">
-        <v>0.1863576</v>
+        <v>0.2530528</v>
       </c>
       <c r="N5">
-        <v>1.130309066666667</v>
+        <v>1.063613866666667</v>
       </c>
       <c r="O5">
-        <v>0.2486679946666668</v>
+        <v>0.2339950506666668</v>
       </c>
       <c r="P5">
-        <v>0.8816410720000005</v>
+        <v>0.8296188160000004</v>
       </c>
       <c r="Q5">
-        <v>5.481641072</v>
+        <v>5.429618816</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07913547602924004</v>
+        <v>0.07940812626352389</v>
       </c>
       <c r="T5">
-        <v>0.769872425617553</v>
+        <v>0.7761691977719144</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>7.065269496208725</v>
+        <v>5.203130203130205</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07795716121298293</v>
+        <v>0.07809289067760301</v>
       </c>
       <c r="C6">
-        <v>101.7337076911483</v>
+        <v>100.1685607329591</v>
       </c>
       <c r="D6">
-        <v>100.1997076911483</v>
+        <v>99.77856073295912</v>
       </c>
       <c r="E6">
-        <v>-36.024</v>
+        <v>-34.88</v>
       </c>
       <c r="F6">
-        <v>4.576000000000001</v>
+        <v>5.720000000000001</v>
       </c>
       <c r="G6">
         <v>6.11</v>
@@ -1767,45 +1767,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M6">
-        <v>0.2530528</v>
+        <v>0.3506360000000001</v>
       </c>
       <c r="N6">
-        <v>1.063613866666667</v>
+        <v>0.9660306666666673</v>
       </c>
       <c r="O6">
-        <v>0.2339950506666668</v>
+        <v>0.2125267466666668</v>
       </c>
       <c r="P6">
-        <v>0.8296188160000004</v>
+        <v>0.7535039200000004</v>
       </c>
       <c r="Q6">
-        <v>5.429618816</v>
+        <v>5.35350392</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07940812626352389</v>
+        <v>0.07968651650274003</v>
       </c>
       <c r="T6">
-        <v>0.7761691977719144</v>
+        <v>0.7825985335505782</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04313400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>5.203130203130205</v>
+        <v>3.755081242846334</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07809289067760301</v>
+        <v>0.07853750014222313</v>
       </c>
       <c r="C7">
-        <v>100.1685607329591</v>
+        <v>97.66946360351059</v>
       </c>
       <c r="D7">
-        <v>99.77856073295912</v>
+        <v>98.4234636035106</v>
       </c>
       <c r="E7">
-        <v>-34.88</v>
+        <v>-33.736</v>
       </c>
       <c r="F7">
-        <v>5.720000000000001</v>
+        <v>6.864000000000001</v>
       </c>
       <c r="G7">
         <v>6.11</v>
@@ -1849,45 +1849,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M7">
-        <v>0.3506360000000001</v>
+        <v>0.4935216000000001</v>
       </c>
       <c r="N7">
-        <v>0.9660306666666673</v>
+        <v>0.8231450666666672</v>
       </c>
       <c r="O7">
-        <v>0.2125267466666668</v>
+        <v>0.1810919146666668</v>
       </c>
       <c r="P7">
-        <v>0.7535039200000004</v>
+        <v>0.6420531520000003</v>
       </c>
       <c r="Q7">
-        <v>5.35350392</v>
+        <v>5.242053152</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07968651650274003</v>
+        <v>0.07997082993853524</v>
       </c>
       <c r="T7">
-        <v>0.7825985335505782</v>
+        <v>0.7891646637075113</v>
       </c>
       <c r="U7">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.047814</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.755081242846334</v>
+        <v>2.667900790293002</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07853750014222313</v>
+        <v>0.07878164960684322</v>
       </c>
       <c r="C8">
-        <v>97.66946360351059</v>
+        <v>95.79687554829501</v>
       </c>
       <c r="D8">
-        <v>98.4234636035106</v>
+        <v>97.694875548295</v>
       </c>
       <c r="E8">
-        <v>-33.736</v>
+        <v>-32.592</v>
       </c>
       <c r="F8">
-        <v>6.864</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="G8">
         <v>6.11</v>
@@ -1931,45 +1931,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M8">
-        <v>0.4935216</v>
+        <v>0.6070063999999999</v>
       </c>
       <c r="N8">
-        <v>0.8231450666666673</v>
+        <v>0.7096602666666674</v>
       </c>
       <c r="O8">
-        <v>0.1810919146666668</v>
+        <v>0.1561252586666668</v>
       </c>
       <c r="P8">
-        <v>0.6420531520000006</v>
+        <v>0.5535350080000006</v>
       </c>
       <c r="Q8">
-        <v>5.242053152</v>
+        <v>5.153535008</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07997082993853524</v>
+        <v>0.08026125764176689</v>
       </c>
       <c r="T8">
-        <v>0.7891646637075113</v>
+        <v>0.7958720009645935</v>
       </c>
       <c r="U8">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.667900790293003</v>
+        <v>2.16911496594874</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07878164960684322</v>
+        <v>0.07972935907146332</v>
       </c>
       <c r="C9">
-        <v>95.79687554829501</v>
+        <v>91.92407781277065</v>
       </c>
       <c r="D9">
-        <v>97.694875548295</v>
+        <v>94.96607781277065</v>
       </c>
       <c r="E9">
-        <v>-32.592</v>
+        <v>-31.448</v>
       </c>
       <c r="F9">
-        <v>8.008000000000001</v>
+        <v>9.152000000000001</v>
       </c>
       <c r="G9">
         <v>6.11</v>
@@ -2013,45 +2013,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M9">
-        <v>0.6070064000000002</v>
+        <v>0.8236800000000001</v>
       </c>
       <c r="N9">
-        <v>0.7096602666666671</v>
+        <v>0.4929866666666672</v>
       </c>
       <c r="O9">
-        <v>0.1561252586666668</v>
+        <v>0.1084570666666668</v>
       </c>
       <c r="P9">
-        <v>0.5535350080000003</v>
+        <v>0.3845296000000005</v>
       </c>
       <c r="Q9">
-        <v>5.153535008</v>
+        <v>4.9845296</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08026125764176691</v>
+        <v>0.080557998990721</v>
       </c>
       <c r="T9">
-        <v>0.7958720009645937</v>
+        <v>0.8027251499011777</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.169114965948739</v>
+        <v>1.598517223517224</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07972935907146332</v>
+        <v>0.08434675552329018</v>
       </c>
       <c r="C10">
-        <v>91.92407781277065</v>
+        <v>79.40438549356472</v>
       </c>
       <c r="D10">
-        <v>94.96607781277065</v>
+        <v>83.59038549356472</v>
       </c>
       <c r="E10">
-        <v>-31.448</v>
+        <v>-30.304</v>
       </c>
       <c r="F10">
-        <v>9.152000000000001</v>
+        <v>10.296</v>
       </c>
       <c r="G10">
         <v>6.11</v>
@@ -2095,45 +2095,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M10">
-        <v>0.8236800000000001</v>
+        <v>1.5114528</v>
       </c>
       <c r="N10">
-        <v>0.4929866666666672</v>
+        <v>-0.1947861333333327</v>
       </c>
       <c r="O10">
-        <v>0.1084570666666668</v>
+        <v>-0.0428529493333332</v>
       </c>
       <c r="P10">
-        <v>0.3845296000000005</v>
+        <v>-0.1519331839999995</v>
       </c>
       <c r="Q10">
-        <v>4.9845296</v>
+        <v>4.448066816</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.080557998990721</v>
+        <v>0.08095253495092468</v>
       </c>
       <c r="T10">
-        <v>0.8027251499011777</v>
+        <v>0.8118368348943344</v>
       </c>
       <c r="U10">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V10">
-        <v>0.22</v>
+        <v>0.1916478415116018</v>
       </c>
       <c r="W10">
-        <v>0.0702</v>
+        <v>0.1186660968660969</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y10">
-        <v>1.598517223517224</v>
+        <v>0.8711265523254628</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08434675552329018</v>
+        <v>0.0909077394558335</v>
       </c>
       <c r="C11">
-        <v>79.40438549356472</v>
+        <v>66.10204675270693</v>
       </c>
       <c r="D11">
-        <v>83.59038549356472</v>
+        <v>71.43204675270692</v>
       </c>
       <c r="E11">
-        <v>-30.304</v>
+        <v>-29.16</v>
       </c>
       <c r="F11">
-        <v>10.296</v>
+        <v>11.44</v>
       </c>
       <c r="G11">
         <v>6.11</v>
@@ -2177,45 +2177,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M11">
-        <v>1.5114528</v>
+        <v>2.297152</v>
       </c>
       <c r="N11">
-        <v>-0.1947861333333327</v>
+        <v>-0.9804853333333328</v>
       </c>
       <c r="O11">
-        <v>-0.0428529493333332</v>
+        <v>-0.2157067733333332</v>
       </c>
       <c r="P11">
-        <v>-0.1519331839999995</v>
+        <v>-0.7647785599999996</v>
       </c>
       <c r="Q11">
-        <v>4.448066816</v>
+        <v>3.83522144</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08095253495092468</v>
+        <v>0.08151087859764976</v>
       </c>
       <c r="T11">
-        <v>0.8118368348943344</v>
+        <v>0.8247316073360221</v>
       </c>
       <c r="U11">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.1916478415116018</v>
+        <v>0.1260981714168966</v>
       </c>
       <c r="W11">
-        <v>0.1186660968660969</v>
+        <v>0.1754794871794872</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.8711265523254628</v>
+        <v>0.573173506440439</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09090773945583351</v>
+        <v>0.09245773945583351</v>
       </c>
       <c r="C12">
-        <v>66.1020467527069</v>
+        <v>62.58502839052279</v>
       </c>
       <c r="D12">
-        <v>71.4320467527069</v>
+        <v>69.0590283905228</v>
       </c>
       <c r="E12">
-        <v>-29.16</v>
+        <v>-28.016</v>
       </c>
       <c r="F12">
-        <v>11.44</v>
+        <v>12.584</v>
       </c>
       <c r="G12">
         <v>6.11</v>
@@ -2259,37 +2259,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M12">
-        <v>2.297152000000001</v>
+        <v>2.5268672</v>
       </c>
       <c r="N12">
-        <v>-0.9804853333333332</v>
+        <v>-1.210200533333333</v>
       </c>
       <c r="O12">
-        <v>-0.2157067733333333</v>
+        <v>-0.2662441173333333</v>
       </c>
       <c r="P12">
-        <v>-0.7647785599999999</v>
+        <v>-0.9439564159999998</v>
       </c>
       <c r="Q12">
-        <v>3.83522144</v>
+        <v>3.656043584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08151087859764976</v>
+        <v>0.08191212442458964</v>
       </c>
       <c r="T12">
-        <v>0.8247316073360221</v>
+        <v>0.8339982546094606</v>
       </c>
       <c r="U12">
         <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1260981714168966</v>
+        <v>0.1146347012880878</v>
       </c>
       <c r="W12">
-        <v>0.1754794871794872</v>
+        <v>0.177781351981352</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.5731735064404389</v>
+        <v>0.5210668240367626</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09245773945583351</v>
+        <v>0.09826866329629838</v>
       </c>
       <c r="C13">
-        <v>62.58502839052279</v>
+        <v>53.7927154878737</v>
       </c>
       <c r="D13">
-        <v>69.0590283905228</v>
+        <v>61.41071548787369</v>
       </c>
       <c r="E13">
-        <v>-28.016</v>
+        <v>-26.872</v>
       </c>
       <c r="F13">
-        <v>12.584</v>
+        <v>13.728</v>
       </c>
       <c r="G13">
         <v>6.11</v>
@@ -2341,45 +2341,45 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M13">
-        <v>2.5268672</v>
+        <v>3.2370624</v>
       </c>
       <c r="N13">
-        <v>-1.210200533333333</v>
+        <v>-1.920395733333333</v>
       </c>
       <c r="O13">
-        <v>-0.2662441173333333</v>
+        <v>-0.4224870613333332</v>
       </c>
       <c r="P13">
-        <v>-0.9439564159999998</v>
+        <v>-1.497908672</v>
       </c>
       <c r="Q13">
-        <v>3.656043584</v>
+        <v>3.102091328</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08191212442458964</v>
+        <v>0.08239172111176099</v>
       </c>
       <c r="T13">
-        <v>0.8339982546094606</v>
+        <v>0.8450743905718475</v>
       </c>
       <c r="U13">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.1146347012880878</v>
+        <v>0.08948442472615505</v>
       </c>
       <c r="W13">
-        <v>0.177781351981352</v>
+        <v>0.2146995726495727</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.5210668240367626</v>
+        <v>0.4067473851188865</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09826866329629838</v>
+        <v>0.1001686632962984</v>
       </c>
       <c r="C14">
-        <v>53.7927154878737</v>
+        <v>50.50261969752704</v>
       </c>
       <c r="D14">
-        <v>61.41071548787369</v>
+        <v>59.26461969752704</v>
       </c>
       <c r="E14">
-        <v>-26.872</v>
+        <v>-25.728</v>
       </c>
       <c r="F14">
-        <v>13.728</v>
+        <v>14.872</v>
       </c>
       <c r="G14">
         <v>6.11</v>
@@ -2423,37 +2423,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M14">
-        <v>3.2370624</v>
+        <v>3.506817600000001</v>
       </c>
       <c r="N14">
-        <v>-1.920395733333333</v>
+        <v>-2.190150933333333</v>
       </c>
       <c r="O14">
-        <v>-0.4224870613333332</v>
+        <v>-0.4818332053333333</v>
       </c>
       <c r="P14">
-        <v>-1.497908672</v>
+        <v>-1.708317728</v>
       </c>
       <c r="Q14">
-        <v>3.102091328</v>
+        <v>2.891682272</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08239172111176099</v>
+        <v>0.08281231560729849</v>
       </c>
       <c r="T14">
-        <v>0.8450743905718475</v>
+        <v>0.8547878893140528</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.08948442472615505</v>
+        <v>0.08260100743952772</v>
       </c>
       <c r="W14">
-        <v>0.2146995726495727</v>
+        <v>0.2163226824457594</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.4067473851188865</v>
+        <v>0.375459124725126</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1001686632962984</v>
+        <v>0.1020686632962984</v>
       </c>
       <c r="C15">
-        <v>50.50261969752704</v>
+        <v>47.35745651310306</v>
       </c>
       <c r="D15">
-        <v>59.26461969752704</v>
+        <v>57.26345651310306</v>
       </c>
       <c r="E15">
-        <v>-25.728</v>
+        <v>-24.584</v>
       </c>
       <c r="F15">
-        <v>14.872</v>
+        <v>16.016</v>
       </c>
       <c r="G15">
         <v>6.11</v>
@@ -2505,37 +2505,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M15">
-        <v>3.506817600000001</v>
+        <v>3.776572800000001</v>
       </c>
       <c r="N15">
-        <v>-2.190150933333333</v>
+        <v>-2.459906133333333</v>
       </c>
       <c r="O15">
-        <v>-0.4818332053333333</v>
+        <v>-0.5411793493333333</v>
       </c>
       <c r="P15">
-        <v>-1.708317728</v>
+        <v>-1.918726784</v>
       </c>
       <c r="Q15">
-        <v>2.891682272</v>
+        <v>2.681273216</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08281231560729849</v>
+        <v>0.08324269137017404</v>
       </c>
       <c r="T15">
-        <v>0.8547878893140528</v>
+        <v>0.864727283375844</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.08260100743952772</v>
+        <v>0.07670093547956146</v>
       </c>
       <c r="W15">
-        <v>0.2163226824457594</v>
+        <v>0.2177139194139194</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.375459124725126</v>
+        <v>0.3486406158161884</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1020686632962984</v>
+        <v>0.1039686632962984</v>
       </c>
       <c r="C16">
-        <v>47.35745651310306</v>
+        <v>44.34302385728133</v>
       </c>
       <c r="D16">
-        <v>57.26345651310306</v>
+        <v>55.39302385728134</v>
       </c>
       <c r="E16">
-        <v>-24.584</v>
+        <v>-23.44</v>
       </c>
       <c r="F16">
-        <v>16.016</v>
+        <v>17.16</v>
       </c>
       <c r="G16">
         <v>6.11</v>
@@ -2587,37 +2587,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M16">
-        <v>3.776572800000001</v>
+        <v>4.046328000000001</v>
       </c>
       <c r="N16">
-        <v>-2.459906133333333</v>
+        <v>-2.729661333333333</v>
       </c>
       <c r="O16">
-        <v>-0.5411793493333333</v>
+        <v>-0.6005254933333334</v>
       </c>
       <c r="P16">
-        <v>-1.918726784</v>
+        <v>-2.12913584</v>
       </c>
       <c r="Q16">
-        <v>2.681273216</v>
+        <v>2.47086416</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08324269137017404</v>
+        <v>0.08368319362158785</v>
       </c>
       <c r="T16">
-        <v>0.864727283375844</v>
+        <v>0.8749005455332068</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07670093547956146</v>
+        <v>0.07158753978092403</v>
       </c>
       <c r="W16">
-        <v>0.2177139194139194</v>
+        <v>0.2189196581196581</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3486406158161884</v>
+        <v>0.3253979080951092</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1039686632962984</v>
+        <v>0.1058686632962984</v>
       </c>
       <c r="C17">
-        <v>44.34302385728134</v>
+        <v>41.4469165262144</v>
       </c>
       <c r="D17">
-        <v>55.39302385728134</v>
+        <v>53.6409165262144</v>
       </c>
       <c r="E17">
-        <v>-23.44</v>
+        <v>-22.296</v>
       </c>
       <c r="F17">
-        <v>17.16</v>
+        <v>18.304</v>
       </c>
       <c r="G17">
         <v>6.11</v>
@@ -2669,37 +2669,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M17">
-        <v>4.046328</v>
+        <v>4.3160832</v>
       </c>
       <c r="N17">
-        <v>-2.729661333333333</v>
+        <v>-2.999416533333333</v>
       </c>
       <c r="O17">
-        <v>-0.6005254933333332</v>
+        <v>-0.6598716373333333</v>
       </c>
       <c r="P17">
-        <v>-2.12913584</v>
+        <v>-2.339544896</v>
       </c>
       <c r="Q17">
-        <v>2.47086416</v>
+        <v>2.260455104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08368319362158785</v>
+        <v>0.08413418402184486</v>
       </c>
       <c r="T17">
-        <v>0.8749005455332068</v>
+        <v>0.885316028218126</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.07158753978092404</v>
+        <v>0.06711331854461627</v>
       </c>
       <c r="W17">
-        <v>0.2189196581196581</v>
+        <v>0.2199746794871795</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3253979080951093</v>
+        <v>0.305060538839165</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1058686632962984</v>
+        <v>0.1077686632962984</v>
       </c>
       <c r="C18">
-        <v>41.4469165262144</v>
+        <v>38.6582507229116</v>
       </c>
       <c r="D18">
-        <v>53.6409165262144</v>
+        <v>51.99625072291161</v>
       </c>
       <c r="E18">
-        <v>-22.296</v>
+        <v>-21.152</v>
       </c>
       <c r="F18">
-        <v>18.304</v>
+        <v>19.448</v>
       </c>
       <c r="G18">
         <v>6.11</v>
@@ -2751,37 +2751,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M18">
-        <v>4.3160832</v>
+        <v>4.585838400000001</v>
       </c>
       <c r="N18">
-        <v>-2.999416533333333</v>
+        <v>-3.269171733333334</v>
       </c>
       <c r="O18">
-        <v>-0.6598716373333333</v>
+        <v>-0.7192177813333334</v>
       </c>
       <c r="P18">
-        <v>-2.339544896</v>
+        <v>-2.549953952</v>
       </c>
       <c r="Q18">
-        <v>2.260455104</v>
+        <v>2.050046048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08413418402184486</v>
+        <v>0.08459604166066226</v>
       </c>
       <c r="T18">
-        <v>0.885316028218126</v>
+        <v>0.8959824863894288</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06711331854461627</v>
+        <v>0.06316547627728591</v>
       </c>
       <c r="W18">
-        <v>0.2199746794871795</v>
+        <v>0.220905580693816</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.305060538839165</v>
+        <v>0.2871158012603905</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1077686632962984</v>
+        <v>0.1096686632962984</v>
       </c>
       <c r="C19">
-        <v>38.6582507229116</v>
+        <v>35.96743775901389</v>
       </c>
       <c r="D19">
-        <v>51.99625072291161</v>
+        <v>50.44943775901389</v>
       </c>
       <c r="E19">
-        <v>-21.152</v>
+        <v>-20.008</v>
       </c>
       <c r="F19">
-        <v>19.448</v>
+        <v>20.592</v>
       </c>
       <c r="G19">
         <v>6.11</v>
@@ -2833,37 +2833,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M19">
-        <v>4.585838400000001</v>
+        <v>4.855593600000001</v>
       </c>
       <c r="N19">
-        <v>-3.269171733333334</v>
+        <v>-3.538926933333333</v>
       </c>
       <c r="O19">
-        <v>-0.7192177813333334</v>
+        <v>-0.7785639253333333</v>
       </c>
       <c r="P19">
-        <v>-2.549953952</v>
+        <v>-2.760363008</v>
       </c>
       <c r="Q19">
-        <v>2.050046048</v>
+        <v>1.839636992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08459604166066226</v>
+        <v>0.08506916411993863</v>
       </c>
       <c r="T19">
-        <v>0.8959824863894288</v>
+        <v>0.9069091020771047</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06316547627728591</v>
+        <v>0.05965628315077003</v>
       </c>
       <c r="W19">
-        <v>0.220905580693816</v>
+        <v>0.2217330484330484</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2871158012603905</v>
+        <v>0.271164923412591</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1096686632962984</v>
+        <v>0.1115686632962984</v>
       </c>
       <c r="C20">
-        <v>35.96743775901389</v>
+        <v>33.36599698193302</v>
       </c>
       <c r="D20">
-        <v>50.44943775901389</v>
+        <v>48.99199698193302</v>
       </c>
       <c r="E20">
-        <v>-20.008</v>
+        <v>-18.864</v>
       </c>
       <c r="F20">
-        <v>20.592</v>
+        <v>21.736</v>
       </c>
       <c r="G20">
         <v>6.11</v>
@@ -2915,37 +2915,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M20">
-        <v>4.8555936</v>
+        <v>5.1253488</v>
       </c>
       <c r="N20">
-        <v>-3.538926933333332</v>
+        <v>-3.808682133333333</v>
       </c>
       <c r="O20">
-        <v>-0.7785639253333332</v>
+        <v>-0.8379100693333332</v>
       </c>
       <c r="P20">
-        <v>-2.760363007999999</v>
+        <v>-2.970772064</v>
       </c>
       <c r="Q20">
-        <v>1.839636992</v>
+        <v>1.629227936</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08506916411993863</v>
+        <v>0.08555396861524651</v>
       </c>
       <c r="T20">
-        <v>0.9069091020771046</v>
+        <v>0.9181055107447232</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05965628315077004</v>
+        <v>0.05651647877441372</v>
       </c>
       <c r="W20">
-        <v>0.2217330484330484</v>
+        <v>0.2224734143049933</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2711649234125911</v>
+        <v>0.2568930853382442</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1115686632962984</v>
+        <v>0.1134686632962984</v>
       </c>
       <c r="C21">
-        <v>33.36599698193302</v>
+        <v>30.84640021776931</v>
       </c>
       <c r="D21">
-        <v>48.99199698193302</v>
+        <v>47.61640021776931</v>
       </c>
       <c r="E21">
-        <v>-18.864</v>
+        <v>-17.72</v>
       </c>
       <c r="F21">
-        <v>21.736</v>
+        <v>22.88</v>
       </c>
       <c r="G21">
         <v>6.11</v>
@@ -2997,37 +2997,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M21">
-        <v>5.1253488</v>
+        <v>5.395104000000001</v>
       </c>
       <c r="N21">
-        <v>-3.808682133333333</v>
+        <v>-4.078437333333333</v>
       </c>
       <c r="O21">
-        <v>-0.8379100693333332</v>
+        <v>-0.8972562133333334</v>
       </c>
       <c r="P21">
-        <v>-2.970772064</v>
+        <v>-3.18118112</v>
       </c>
       <c r="Q21">
-        <v>1.629227936</v>
+        <v>1.418818879999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08555396861524651</v>
+        <v>0.0860508932229371</v>
       </c>
       <c r="T21">
-        <v>0.9181055107447232</v>
+        <v>0.9295818296290324</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05651647877441372</v>
+        <v>0.05369065483569303</v>
       </c>
       <c r="W21">
-        <v>0.2224734143049933</v>
+        <v>0.2231397435897436</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2568930853382442</v>
+        <v>0.2440484310713319</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1134686632962984</v>
+        <v>0.1153686632962984</v>
       </c>
       <c r="C22">
-        <v>30.84640021776931</v>
+        <v>28.40194170488342</v>
       </c>
       <c r="D22">
-        <v>47.61640021776931</v>
+        <v>46.31594170488343</v>
       </c>
       <c r="E22">
-        <v>-17.72</v>
+        <v>-16.576</v>
       </c>
       <c r="F22">
-        <v>22.88</v>
+        <v>24.024</v>
       </c>
       <c r="G22">
         <v>6.11</v>
@@ -3079,37 +3079,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M22">
-        <v>5.395104000000001</v>
+        <v>5.664859200000001</v>
       </c>
       <c r="N22">
-        <v>-4.078437333333333</v>
+        <v>-4.348192533333334</v>
       </c>
       <c r="O22">
-        <v>-0.8972562133333334</v>
+        <v>-0.9566023573333334</v>
       </c>
       <c r="P22">
-        <v>-3.18118112</v>
+        <v>-3.391590176000001</v>
       </c>
       <c r="Q22">
-        <v>1.418818879999999</v>
+        <v>1.208409823999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0860508932229371</v>
+        <v>0.08656039820044263</v>
       </c>
       <c r="T22">
-        <v>0.9295818296290324</v>
+        <v>0.9413486882319314</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05369065483569303</v>
+        <v>0.0511339569863743</v>
       </c>
       <c r="W22">
-        <v>0.2231397435897436</v>
+        <v>0.2237426129426129</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2440484310713319</v>
+        <v>0.2324270772107923</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1153686632962984</v>
+        <v>0.1172686632962984</v>
       </c>
       <c r="C23">
-        <v>28.40194170488345</v>
+        <v>26.02662877442548</v>
       </c>
       <c r="D23">
-        <v>46.31594170488345</v>
+        <v>45.08462877442548</v>
       </c>
       <c r="E23">
-        <v>-16.576</v>
+        <v>-15.432</v>
       </c>
       <c r="F23">
-        <v>24.024</v>
+        <v>25.168</v>
       </c>
       <c r="G23">
         <v>6.11</v>
@@ -3161,37 +3161,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M23">
-        <v>5.6648592</v>
+        <v>5.934614400000001</v>
       </c>
       <c r="N23">
-        <v>-4.348192533333333</v>
+        <v>-4.617947733333334</v>
       </c>
       <c r="O23">
-        <v>-0.9566023573333333</v>
+        <v>-1.015948501333333</v>
       </c>
       <c r="P23">
-        <v>-3.391590176</v>
+        <v>-3.601999232</v>
       </c>
       <c r="Q23">
-        <v>1.208409824</v>
+        <v>0.9980007679999994</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08656039820044263</v>
+        <v>0.08708296740814062</v>
       </c>
       <c r="T23">
-        <v>0.9413486882319314</v>
+        <v>0.9534172611579819</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05113395698637431</v>
+        <v>0.04880968621426638</v>
       </c>
       <c r="W23">
-        <v>0.2237426129426129</v>
+        <v>0.224290675990676</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2324270772107924</v>
+        <v>0.2218622100648472</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1172686632962984</v>
+        <v>0.1191686632962984</v>
       </c>
       <c r="C24">
-        <v>26.02662877442548</v>
+        <v>23.71508951688893</v>
       </c>
       <c r="D24">
-        <v>45.08462877442548</v>
+        <v>43.91708951688894</v>
       </c>
       <c r="E24">
-        <v>-15.432</v>
+        <v>-14.288</v>
       </c>
       <c r="F24">
-        <v>25.168</v>
+        <v>26.312</v>
       </c>
       <c r="G24">
         <v>6.11</v>
@@ -3243,37 +3243,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M24">
-        <v>5.934614400000001</v>
+        <v>6.204369600000001</v>
       </c>
       <c r="N24">
-        <v>-4.617947733333334</v>
+        <v>-4.887702933333333</v>
       </c>
       <c r="O24">
-        <v>-1.015948501333333</v>
+        <v>-1.075294645333333</v>
       </c>
       <c r="P24">
-        <v>-3.601999232</v>
+        <v>-3.812408288</v>
       </c>
       <c r="Q24">
-        <v>0.9980007679999994</v>
+        <v>0.7875917119999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08708296740814062</v>
+        <v>0.08761910984201257</v>
       </c>
       <c r="T24">
-        <v>0.9534172611579819</v>
+        <v>0.9657993035106829</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04880968621426638</v>
+        <v>0.04668752594408089</v>
       </c>
       <c r="W24">
-        <v>0.224290675990676</v>
+        <v>0.2247910813823857</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2218622100648472</v>
+        <v>0.2122160270185495</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1191686632962984</v>
+        <v>0.1210686632962984</v>
       </c>
       <c r="C25">
-        <v>23.71508951688893</v>
+        <v>21.4624944332535</v>
       </c>
       <c r="D25">
-        <v>43.91708951688894</v>
+        <v>42.8084944332535</v>
       </c>
       <c r="E25">
-        <v>-14.288</v>
+        <v>-13.144</v>
       </c>
       <c r="F25">
-        <v>26.312</v>
+        <v>27.456</v>
       </c>
       <c r="G25">
         <v>6.11</v>
@@ -3325,37 +3325,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M25">
-        <v>6.204369600000001</v>
+        <v>6.474124800000001</v>
       </c>
       <c r="N25">
-        <v>-4.887702933333333</v>
+        <v>-5.157458133333334</v>
       </c>
       <c r="O25">
-        <v>-1.075294645333333</v>
+        <v>-1.134640789333333</v>
       </c>
       <c r="P25">
-        <v>-3.812408288</v>
+        <v>-4.022817344</v>
       </c>
       <c r="Q25">
-        <v>0.7875917119999998</v>
+        <v>0.5771826559999997</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08761910984201257</v>
+        <v>0.08816936128730221</v>
       </c>
       <c r="T25">
-        <v>0.9657993035106829</v>
+        <v>0.9785071890831919</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04668752594408089</v>
+        <v>0.04474221236307752</v>
       </c>
       <c r="W25">
-        <v>0.2247910813823857</v>
+        <v>0.2252497863247863</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2122160270185495</v>
+        <v>0.2033736925594433</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1210686632962984</v>
+        <v>0.1229686632962984</v>
       </c>
       <c r="C26">
-        <v>21.46249443325349</v>
+        <v>19.26448966047568</v>
       </c>
       <c r="D26">
-        <v>42.80849443325349</v>
+        <v>41.75448966047568</v>
       </c>
       <c r="E26">
-        <v>-13.144</v>
+        <v>-12</v>
       </c>
       <c r="F26">
-        <v>27.456</v>
+        <v>28.6</v>
       </c>
       <c r="G26">
         <v>6.11</v>
@@ -3407,37 +3407,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M26">
-        <v>6.4741248</v>
+        <v>6.743880000000001</v>
       </c>
       <c r="N26">
-        <v>-5.157458133333333</v>
+        <v>-5.427213333333333</v>
       </c>
       <c r="O26">
-        <v>-1.134640789333333</v>
+        <v>-1.193986933333333</v>
       </c>
       <c r="P26">
-        <v>-4.022817344</v>
+        <v>-4.2332264</v>
       </c>
       <c r="Q26">
-        <v>0.5771826559999997</v>
+        <v>0.3667735999999993</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08816936128730221</v>
+        <v>0.08873428610446624</v>
       </c>
       <c r="T26">
-        <v>0.9785071890831919</v>
+        <v>0.991553951604301</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04474221236307752</v>
+        <v>0.04295252386855442</v>
       </c>
       <c r="W26">
-        <v>0.2252497863247863</v>
+        <v>0.2256717948717949</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2033736925594433</v>
+        <v>0.1952387448570655</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1229686632962984</v>
+        <v>0.1248686632962984</v>
       </c>
       <c r="C27">
-        <v>19.26448966047568</v>
+        <v>17.11713982442733</v>
       </c>
       <c r="D27">
-        <v>41.75448966047568</v>
+        <v>40.75113982442733</v>
       </c>
       <c r="E27">
-        <v>-12</v>
+        <v>-10.856</v>
       </c>
       <c r="F27">
-        <v>28.6</v>
+        <v>29.744</v>
       </c>
       <c r="G27">
         <v>6.11</v>
@@ -3489,37 +3489,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M27">
-        <v>6.743880000000001</v>
+        <v>7.013635200000001</v>
       </c>
       <c r="N27">
-        <v>-5.427213333333333</v>
+        <v>-5.696968533333334</v>
       </c>
       <c r="O27">
-        <v>-1.193986933333333</v>
+        <v>-1.253333077333334</v>
       </c>
       <c r="P27">
-        <v>-4.2332264</v>
+        <v>-4.443635456000001</v>
       </c>
       <c r="Q27">
-        <v>0.3667735999999993</v>
+        <v>0.1563645439999988</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08873428610446624</v>
+        <v>0.08931447915993199</v>
       </c>
       <c r="T27">
-        <v>0.991553951604301</v>
+        <v>1.004953329328683</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04295252386855442</v>
+        <v>0.04130050371976386</v>
       </c>
       <c r="W27">
-        <v>0.2256717948717949</v>
+        <v>0.2260613412228797</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1952387448570655</v>
+        <v>0.187729562362563</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1248686632962984</v>
+        <v>0.1267686632962984</v>
       </c>
       <c r="C28">
-        <v>17.11713982442733</v>
+        <v>15.01687893886628</v>
       </c>
       <c r="D28">
-        <v>40.75113982442733</v>
+        <v>39.79487893886628</v>
       </c>
       <c r="E28">
-        <v>-10.856</v>
+        <v>-9.711999999999996</v>
       </c>
       <c r="F28">
-        <v>29.744</v>
+        <v>30.88800000000001</v>
       </c>
       <c r="G28">
         <v>6.11</v>
@@ -3571,37 +3571,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M28">
-        <v>7.013635200000001</v>
+        <v>7.283390400000002</v>
       </c>
       <c r="N28">
-        <v>-5.696968533333334</v>
+        <v>-5.966723733333335</v>
       </c>
       <c r="O28">
-        <v>-1.253333077333334</v>
+        <v>-1.312679221333334</v>
       </c>
       <c r="P28">
-        <v>-4.443635456000001</v>
+        <v>-4.654044512</v>
       </c>
       <c r="Q28">
-        <v>0.1563645439999988</v>
+        <v>-0.05404451200000082</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08931447915993199</v>
+        <v>0.08991056791554751</v>
       </c>
       <c r="T28">
-        <v>1.004953329328683</v>
+        <v>1.01871981329209</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04130050371976386</v>
+        <v>0.03977085543384668</v>
       </c>
       <c r="W28">
-        <v>0.2260613412228797</v>
+        <v>0.2264220322886989</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.187729562362563</v>
+        <v>0.180776615608394</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1267686632962984</v>
+        <v>0.1286686632962984</v>
       </c>
       <c r="C29">
-        <v>15.01687893886628</v>
+        <v>12.96046805909259</v>
       </c>
       <c r="D29">
-        <v>39.79487893886628</v>
+        <v>38.8824680590926</v>
       </c>
       <c r="E29">
-        <v>-9.711999999999996</v>
+        <v>-8.567999999999998</v>
       </c>
       <c r="F29">
-        <v>30.88800000000001</v>
+        <v>32.032</v>
       </c>
       <c r="G29">
         <v>6.11</v>
@@ -3653,37 +3653,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M29">
-        <v>7.283390400000002</v>
+        <v>7.553145600000001</v>
       </c>
       <c r="N29">
-        <v>-5.966723733333335</v>
+        <v>-6.236478933333334</v>
       </c>
       <c r="O29">
-        <v>-1.312679221333334</v>
+        <v>-1.372025365333333</v>
       </c>
       <c r="P29">
-        <v>-4.654044512</v>
+        <v>-4.864453568000001</v>
       </c>
       <c r="Q29">
-        <v>-0.05404451200000082</v>
+        <v>-0.2644535680000013</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08991056791554751</v>
+        <v>0.09052321469215233</v>
       </c>
       <c r="T29">
-        <v>1.01871981329209</v>
+        <v>1.032868699587814</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03977085543384668</v>
+        <v>0.03835046773978073</v>
       </c>
       <c r="W29">
-        <v>0.2264220322886989</v>
+        <v>0.2267569597069597</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.180776615608394</v>
+        <v>0.1743203079080943</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1286686632962984</v>
+        <v>0.1305686632962984</v>
       </c>
       <c r="C30">
-        <v>12.96046805909259</v>
+        <v>10.94495863049573</v>
       </c>
       <c r="D30">
-        <v>38.8824680590926</v>
+        <v>38.01095863049574</v>
       </c>
       <c r="E30">
-        <v>-8.567999999999998</v>
+        <v>-7.423999999999992</v>
       </c>
       <c r="F30">
-        <v>32.032</v>
+        <v>33.17600000000001</v>
       </c>
       <c r="G30">
         <v>6.11</v>
@@ -3735,37 +3735,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M30">
-        <v>7.553145600000001</v>
+        <v>7.822900800000003</v>
       </c>
       <c r="N30">
-        <v>-6.236478933333334</v>
+        <v>-6.506234133333336</v>
       </c>
       <c r="O30">
-        <v>-1.372025365333333</v>
+        <v>-1.431371509333334</v>
       </c>
       <c r="P30">
-        <v>-4.864453568000001</v>
+        <v>-5.074862624000001</v>
       </c>
       <c r="Q30">
-        <v>-0.2644535680000013</v>
+        <v>-0.4748626240000018</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09052321469215233</v>
+        <v>0.09115311912443616</v>
       </c>
       <c r="T30">
-        <v>1.032868699587814</v>
+        <v>1.047416146060882</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03835046773978073</v>
+        <v>0.03702803781771932</v>
       </c>
       <c r="W30">
-        <v>0.2267569597069597</v>
+        <v>0.2270687886825818</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1743203079080943</v>
+        <v>0.1683092628078151</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1305686632962984</v>
+        <v>0.1324686632962984</v>
       </c>
       <c r="C31">
-        <v>10.94495863049573</v>
+        <v>8.96766065806667</v>
       </c>
       <c r="D31">
-        <v>38.01095863049574</v>
+        <v>37.17766065806667</v>
       </c>
       <c r="E31">
-        <v>-7.423999999999999</v>
+        <v>-6.280000000000001</v>
       </c>
       <c r="F31">
-        <v>33.176</v>
+        <v>34.32</v>
       </c>
       <c r="G31">
         <v>6.11</v>
@@ -3817,37 +3817,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M31">
-        <v>7.822900800000001</v>
+        <v>8.092656</v>
       </c>
       <c r="N31">
-        <v>-6.506234133333334</v>
+        <v>-6.775989333333333</v>
       </c>
       <c r="O31">
-        <v>-1.431371509333333</v>
+        <v>-1.490717653333333</v>
       </c>
       <c r="P31">
-        <v>-5.074862624000001</v>
+        <v>-5.285271679999999</v>
       </c>
       <c r="Q31">
-        <v>-0.4748626240000009</v>
+        <v>-0.6852716799999996</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09115311912443616</v>
+        <v>0.09180102082621383</v>
       </c>
       <c r="T31">
-        <v>1.047416146060882</v>
+        <v>1.062379233861751</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03702803781771932</v>
+        <v>0.03579376989046202</v>
       </c>
       <c r="W31">
-        <v>0.2270687886825818</v>
+        <v>0.2273598290598291</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1683092628078151</v>
+        <v>0.1626989540475546</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1324686632962984</v>
+        <v>0.1343686632962984</v>
       </c>
       <c r="C32">
-        <v>8.96766065806667</v>
+        <v>7.026114972929548</v>
       </c>
       <c r="D32">
-        <v>37.17766065806667</v>
+        <v>36.38011497292955</v>
       </c>
       <c r="E32">
-        <v>-6.280000000000001</v>
+        <v>-5.136000000000003</v>
       </c>
       <c r="F32">
-        <v>34.32</v>
+        <v>35.464</v>
       </c>
       <c r="G32">
         <v>6.11</v>
@@ -3899,37 +3899,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M32">
-        <v>8.092656</v>
+        <v>8.3624112</v>
       </c>
       <c r="N32">
-        <v>-6.775989333333333</v>
+        <v>-7.045744533333333</v>
       </c>
       <c r="O32">
-        <v>-1.490717653333333</v>
+        <v>-1.550063797333333</v>
       </c>
       <c r="P32">
-        <v>-5.285271679999999</v>
+        <v>-5.495680736</v>
       </c>
       <c r="Q32">
-        <v>-0.6852716799999996</v>
+        <v>-0.8956807360000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09180102082621383</v>
+        <v>0.09246770228746332</v>
       </c>
       <c r="T32">
-        <v>1.062379233861751</v>
+        <v>1.077776034352501</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03579376989046202</v>
+        <v>0.03463913215206002</v>
       </c>
       <c r="W32">
-        <v>0.2273598290598291</v>
+        <v>0.2276320926385443</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1626989540475546</v>
+        <v>0.1574506006911819</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1343686632962984</v>
+        <v>0.1362686632962984</v>
       </c>
       <c r="C33">
-        <v>7.026114972929548</v>
+        <v>5.118068993581097</v>
       </c>
       <c r="D33">
-        <v>36.38011497292955</v>
+        <v>35.6160689935811</v>
       </c>
       <c r="E33">
-        <v>-5.136000000000003</v>
+        <v>-3.991999999999997</v>
       </c>
       <c r="F33">
-        <v>35.464</v>
+        <v>36.608</v>
       </c>
       <c r="G33">
         <v>6.11</v>
@@ -3981,37 +3981,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M33">
-        <v>8.3624112</v>
+        <v>8.632166400000001</v>
       </c>
       <c r="N33">
-        <v>-7.045744533333333</v>
+        <v>-7.315499733333334</v>
       </c>
       <c r="O33">
-        <v>-1.550063797333333</v>
+        <v>-1.609409941333333</v>
       </c>
       <c r="P33">
-        <v>-5.495680736</v>
+        <v>-5.706089792</v>
       </c>
       <c r="Q33">
-        <v>-0.8956807360000001</v>
+        <v>-1.106089792000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09246770228746332</v>
+        <v>0.09315399202698482</v>
       </c>
       <c r="T33">
-        <v>1.077776034352501</v>
+        <v>1.093625681916509</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03463913215206002</v>
+        <v>0.03355665927230814</v>
       </c>
       <c r="W33">
-        <v>0.2276320926385443</v>
+        <v>0.2278873397435898</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1574506006911819</v>
+        <v>0.1525302694195825</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1362686632962984</v>
+        <v>0.1381686632962984</v>
       </c>
       <c r="C34">
-        <v>5.118068993581097</v>
+        <v>3.24145547864115</v>
       </c>
       <c r="D34">
-        <v>35.6160689935811</v>
+        <v>34.88345547864115</v>
       </c>
       <c r="E34">
-        <v>-3.991999999999997</v>
+        <v>-2.847999999999999</v>
       </c>
       <c r="F34">
-        <v>36.608</v>
+        <v>37.752</v>
       </c>
       <c r="G34">
         <v>6.11</v>
@@ -4063,37 +4063,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M34">
-        <v>8.632166400000001</v>
+        <v>8.901921600000001</v>
       </c>
       <c r="N34">
-        <v>-7.315499733333334</v>
+        <v>-7.585254933333334</v>
       </c>
       <c r="O34">
-        <v>-1.609409941333333</v>
+        <v>-1.668756085333333</v>
       </c>
       <c r="P34">
-        <v>-5.706089792</v>
+        <v>-5.916498848000001</v>
       </c>
       <c r="Q34">
-        <v>-1.106089792000001</v>
+        <v>-1.316498848000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09315399202698482</v>
+        <v>0.09386076802738758</v>
       </c>
       <c r="T34">
-        <v>1.093625681916509</v>
+        <v>1.109948453288397</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03355665927230814</v>
+        <v>0.03253979080951092</v>
       </c>
       <c r="W34">
-        <v>0.2278873397435898</v>
+        <v>0.2281271173271173</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1525302694195825</v>
+        <v>0.1479081400432315</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1381686632962984</v>
+        <v>0.1400686632962984</v>
       </c>
       <c r="C35">
-        <v>3.24145547864115</v>
+        <v>1.394373849053416</v>
       </c>
       <c r="D35">
-        <v>34.88345547864115</v>
+        <v>34.18037384905342</v>
       </c>
       <c r="E35">
-        <v>-2.847999999999999</v>
+        <v>-1.703999999999994</v>
       </c>
       <c r="F35">
-        <v>37.752</v>
+        <v>38.89600000000001</v>
       </c>
       <c r="G35">
         <v>6.11</v>
@@ -4145,37 +4145,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M35">
-        <v>8.901921600000001</v>
+        <v>9.171676800000002</v>
       </c>
       <c r="N35">
-        <v>-7.585254933333334</v>
+        <v>-7.855010133333335</v>
       </c>
       <c r="O35">
-        <v>-1.668756085333333</v>
+        <v>-1.728102229333334</v>
       </c>
       <c r="P35">
-        <v>-5.916498848000001</v>
+        <v>-6.126907904000001</v>
       </c>
       <c r="Q35">
-        <v>-1.316498848000001</v>
+        <v>-1.526907904000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09386076802738758</v>
+        <v>0.09458896148234799</v>
       </c>
       <c r="T35">
-        <v>1.109948453288397</v>
+        <v>1.126765854095797</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03253979080951092</v>
+        <v>0.03158273813864296</v>
       </c>
       <c r="W35">
-        <v>0.2281271173271173</v>
+        <v>0.228352790346908</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1479081400432315</v>
+        <v>0.1435579006301952</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1400686632962984</v>
+        <v>0.1419686632962984</v>
       </c>
       <c r="C36">
-        <v>1.394373849053416</v>
+        <v>-0.4249262756151566</v>
       </c>
       <c r="D36">
-        <v>34.18037384905342</v>
+        <v>33.50507372438485</v>
       </c>
       <c r="E36">
-        <v>-1.703999999999994</v>
+        <v>-0.5599999999999952</v>
       </c>
       <c r="F36">
-        <v>38.89600000000001</v>
+        <v>40.04000000000001</v>
       </c>
       <c r="G36">
         <v>6.11</v>
@@ -4227,37 +4227,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M36">
-        <v>9.171676800000002</v>
+        <v>9.441432000000002</v>
       </c>
       <c r="N36">
-        <v>-7.855010133333335</v>
+        <v>-8.124765333333336</v>
       </c>
       <c r="O36">
-        <v>-1.728102229333334</v>
+        <v>-1.787448373333334</v>
       </c>
       <c r="P36">
-        <v>-6.126907904000001</v>
+        <v>-6.337316960000003</v>
       </c>
       <c r="Q36">
-        <v>-1.526907904000002</v>
+        <v>-1.737316960000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09458896148234799</v>
+        <v>0.09533956088976873</v>
       </c>
       <c r="T36">
-        <v>1.126765854095797</v>
+        <v>1.144100713389578</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03158273813864296</v>
+        <v>0.03068037419182458</v>
       </c>
       <c r="W36">
-        <v>0.228352790346908</v>
+        <v>0.2285655677655678</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1435579006301952</v>
+        <v>0.1394562463264752</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1419686632962984</v>
+        <v>0.1438686632962984</v>
       </c>
       <c r="C37">
-        <v>-0.4249262756151566</v>
+        <v>-2.2180596270507</v>
       </c>
       <c r="D37">
-        <v>33.50507372438485</v>
+        <v>32.85594037294931</v>
       </c>
       <c r="E37">
-        <v>-0.5599999999999952</v>
+        <v>0.5840000000000032</v>
       </c>
       <c r="F37">
-        <v>40.04000000000001</v>
+        <v>41.184</v>
       </c>
       <c r="G37">
         <v>6.11</v>
@@ -4309,37 +4309,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M37">
-        <v>9.441432000000002</v>
+        <v>9.711187200000001</v>
       </c>
       <c r="N37">
-        <v>-8.124765333333336</v>
+        <v>-8.394520533333335</v>
       </c>
       <c r="O37">
-        <v>-1.787448373333334</v>
+        <v>-1.846794517333334</v>
       </c>
       <c r="P37">
-        <v>-6.337316960000003</v>
+        <v>-6.547726016000001</v>
       </c>
       <c r="Q37">
-        <v>-1.737316960000003</v>
+        <v>-1.947726016000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09533956088976873</v>
+        <v>0.09611361652867137</v>
       </c>
       <c r="T37">
-        <v>1.144100713389578</v>
+        <v>1.161977287036291</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03068037419182458</v>
+        <v>0.02982814157538501</v>
       </c>
       <c r="W37">
-        <v>0.2285655677655678</v>
+        <v>0.2287665242165242</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1394562463264752</v>
+        <v>0.1355824617062954</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1438686632962984</v>
+        <v>0.1457686632962984</v>
       </c>
       <c r="C38">
-        <v>-2.218059627050692</v>
+        <v>-3.986518178862866</v>
       </c>
       <c r="D38">
-        <v>32.85594037294931</v>
+        <v>32.23148182113714</v>
       </c>
       <c r="E38">
-        <v>0.5839999999999961</v>
+        <v>1.728000000000002</v>
       </c>
       <c r="F38">
-        <v>41.184</v>
+        <v>42.328</v>
       </c>
       <c r="G38">
         <v>6.11</v>
@@ -4391,37 +4391,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M38">
-        <v>9.711187199999999</v>
+        <v>9.980942400000002</v>
       </c>
       <c r="N38">
-        <v>-8.394520533333331</v>
+        <v>-8.664275733333334</v>
       </c>
       <c r="O38">
-        <v>-1.846794517333333</v>
+        <v>-1.906140661333333</v>
       </c>
       <c r="P38">
-        <v>-6.547726015999999</v>
+        <v>-6.758135072</v>
       </c>
       <c r="Q38">
-        <v>-1.947726015999999</v>
+        <v>-2.158135072</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09611361652867137</v>
+        <v>0.09691224536245981</v>
       </c>
       <c r="T38">
-        <v>1.16197728703629</v>
+        <v>1.180421370957501</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02982814157538502</v>
+        <v>0.02902197558686109</v>
       </c>
       <c r="W38">
-        <v>0.2287665242165242</v>
+        <v>0.2289566181566182</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1355824617062956</v>
+        <v>0.1319180708493687</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1457686632962984</v>
+        <v>0.1476686632962984</v>
       </c>
       <c r="C39">
-        <v>-3.986518178862866</v>
+        <v>-5.731682594675775</v>
       </c>
       <c r="D39">
-        <v>32.23148182113714</v>
+        <v>31.63031740532423</v>
       </c>
       <c r="E39">
-        <v>1.728000000000002</v>
+        <v>2.872</v>
       </c>
       <c r="F39">
-        <v>42.328</v>
+        <v>43.472</v>
       </c>
       <c r="G39">
         <v>6.11</v>
@@ -4473,37 +4473,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M39">
-        <v>9.980942400000002</v>
+        <v>10.2506976</v>
       </c>
       <c r="N39">
-        <v>-8.664275733333334</v>
+        <v>-8.934030933333332</v>
       </c>
       <c r="O39">
-        <v>-1.906140661333333</v>
+        <v>-1.965486805333333</v>
       </c>
       <c r="P39">
-        <v>-6.758135072</v>
+        <v>-6.968544128</v>
       </c>
       <c r="Q39">
-        <v>-2.158135072</v>
+        <v>-2.368544128</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09691224536245981</v>
+        <v>0.09773663641669303</v>
       </c>
       <c r="T39">
-        <v>1.180421370957501</v>
+        <v>1.199460425327784</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02902197558686109</v>
+        <v>0.02825823938720686</v>
       </c>
       <c r="W39">
-        <v>0.2289566181566182</v>
+        <v>0.2291367071524966</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1319180708493687</v>
+        <v>0.1284465426691221</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1476686632962984</v>
+        <v>0.1495686632962984</v>
       </c>
       <c r="C40">
-        <v>-5.731682594675775</v>
+        <v>-7.454832418534593</v>
       </c>
       <c r="D40">
-        <v>31.63031740532423</v>
+        <v>31.05116758146541</v>
       </c>
       <c r="E40">
-        <v>2.872</v>
+        <v>4.016000000000005</v>
       </c>
       <c r="F40">
-        <v>43.472</v>
+        <v>44.61600000000001</v>
       </c>
       <c r="G40">
         <v>6.11</v>
@@ -4555,37 +4555,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M40">
-        <v>10.2506976</v>
+        <v>10.5204528</v>
       </c>
       <c r="N40">
-        <v>-8.934030933333332</v>
+        <v>-9.203786133333335</v>
       </c>
       <c r="O40">
-        <v>-1.965486805333333</v>
+        <v>-2.024832949333334</v>
       </c>
       <c r="P40">
-        <v>-6.968544128</v>
+        <v>-7.178953184000001</v>
       </c>
       <c r="Q40">
-        <v>-2.368544128</v>
+        <v>-2.578953184000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09773663641669303</v>
+        <v>0.09858805668581914</v>
       </c>
       <c r="T40">
-        <v>1.199460425327784</v>
+        <v>1.219123710988895</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02825823938720686</v>
+        <v>0.02753366914650924</v>
       </c>
       <c r="W40">
-        <v>0.2291367071524966</v>
+        <v>0.2293075608152531</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1284465426691221</v>
+        <v>0.125153041575042</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1495686632962984</v>
+        <v>0.1514686632962984</v>
       </c>
       <c r="C41">
-        <v>-7.454832418534593</v>
+        <v>-9.157155165926163</v>
       </c>
       <c r="D41">
-        <v>31.05116758146541</v>
+        <v>30.49284483407384</v>
       </c>
       <c r="E41">
-        <v>4.016000000000005</v>
+        <v>5.160000000000004</v>
       </c>
       <c r="F41">
-        <v>44.61600000000001</v>
+        <v>45.76000000000001</v>
       </c>
       <c r="G41">
         <v>6.11</v>
@@ -4637,37 +4637,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M41">
-        <v>10.5204528</v>
+        <v>10.790208</v>
       </c>
       <c r="N41">
-        <v>-9.203786133333335</v>
+        <v>-9.473541333333333</v>
       </c>
       <c r="O41">
-        <v>-2.024832949333334</v>
+        <v>-2.084179093333333</v>
       </c>
       <c r="P41">
-        <v>-7.178953184000001</v>
+        <v>-7.389362240000001</v>
       </c>
       <c r="Q41">
-        <v>-2.578953184000001</v>
+        <v>-2.789362240000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09858805668581914</v>
+        <v>0.0994678576305828</v>
       </c>
       <c r="T41">
-        <v>1.219123710988895</v>
+        <v>1.239442439505376</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02753366914650924</v>
+        <v>0.02684532741784651</v>
       </c>
       <c r="W41">
-        <v>0.2293075608152531</v>
+        <v>0.2294698717948718</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.125153041575042</v>
+        <v>0.122024215535666</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1514686632962984</v>
+        <v>0.1533686632962984</v>
       </c>
       <c r="C42">
-        <v>-9.157155165926163</v>
+        <v>-10.83975445134401</v>
       </c>
       <c r="D42">
-        <v>30.49284483407384</v>
+        <v>29.95424554865599</v>
       </c>
       <c r="E42">
-        <v>5.160000000000004</v>
+        <v>6.304000000000002</v>
       </c>
       <c r="F42">
-        <v>45.76000000000001</v>
+        <v>46.904</v>
       </c>
       <c r="G42">
         <v>6.11</v>
@@ -4719,37 +4719,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M42">
-        <v>10.790208</v>
+        <v>11.0599632</v>
       </c>
       <c r="N42">
-        <v>-9.473541333333333</v>
+        <v>-9.743296533333336</v>
       </c>
       <c r="O42">
-        <v>-2.084179093333333</v>
+        <v>-2.143525237333334</v>
       </c>
       <c r="P42">
-        <v>-7.389362240000001</v>
+        <v>-7.599771296000002</v>
       </c>
       <c r="Q42">
-        <v>-2.789362240000001</v>
+        <v>-2.999771296000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0994678576305828</v>
+        <v>0.1003774823361859</v>
       </c>
       <c r="T42">
-        <v>1.239442439505376</v>
+        <v>1.260449938480044</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02684532741784651</v>
+        <v>0.0261905633344844</v>
       </c>
       <c r="W42">
-        <v>0.2294698717948718</v>
+        <v>0.2296242651657286</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.122024215535666</v>
+        <v>0.1190480151567472</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1533686632962984</v>
+        <v>0.1552686632962984</v>
       </c>
       <c r="C43">
-        <v>-10.83975445134401</v>
+        <v>-12.50365726945371</v>
       </c>
       <c r="D43">
-        <v>29.95424554865599</v>
+        <v>29.4343427305463</v>
       </c>
       <c r="E43">
-        <v>6.304000000000002</v>
+        <v>7.448000000000008</v>
       </c>
       <c r="F43">
-        <v>46.904</v>
+        <v>48.04800000000001</v>
       </c>
       <c r="G43">
         <v>6.11</v>
@@ -4801,37 +4801,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M43">
-        <v>11.0599632</v>
+        <v>11.3297184</v>
       </c>
       <c r="N43">
-        <v>-9.743296533333336</v>
+        <v>-10.01305173333333</v>
       </c>
       <c r="O43">
-        <v>-2.143525237333334</v>
+        <v>-2.202871381333333</v>
       </c>
       <c r="P43">
-        <v>-7.599771296000002</v>
+        <v>-7.810180352000001</v>
       </c>
       <c r="Q43">
-        <v>-2.999771296000002</v>
+        <v>-3.210180352000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1003774823361859</v>
+        <v>0.1013184734109477</v>
       </c>
       <c r="T43">
-        <v>1.260449938480044</v>
+        <v>1.282181833971079</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0261905633344844</v>
+        <v>0.02556697849318715</v>
       </c>
       <c r="W43">
-        <v>0.2296242651657286</v>
+        <v>0.2297713064713065</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1190480151567472</v>
+        <v>0.1162135386053962</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1552686632962984</v>
+        <v>0.1571686632962984</v>
       </c>
       <c r="C44">
-        <v>-12.5036572694537</v>
+        <v>-14.1498205309382</v>
       </c>
       <c r="D44">
-        <v>29.4343427305463</v>
+        <v>28.9321794690618</v>
       </c>
       <c r="E44">
-        <v>7.448</v>
+        <v>8.591999999999999</v>
       </c>
       <c r="F44">
-        <v>48.048</v>
+        <v>49.192</v>
       </c>
       <c r="G44">
         <v>6.11</v>
@@ -4883,37 +4883,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M44">
-        <v>11.3297184</v>
+        <v>11.5994736</v>
       </c>
       <c r="N44">
-        <v>-10.01305173333333</v>
+        <v>-10.28280693333333</v>
       </c>
       <c r="O44">
-        <v>-2.202871381333333</v>
+        <v>-2.262217525333333</v>
       </c>
       <c r="P44">
-        <v>-7.810180352000001</v>
+        <v>-8.020589407999999</v>
       </c>
       <c r="Q44">
-        <v>-3.210180352000002</v>
+        <v>-3.420589408</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1013184734109477</v>
+        <v>0.1022924817164029</v>
       </c>
       <c r="T44">
-        <v>1.282181833971079</v>
+        <v>1.304676252110923</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02556697849318715</v>
+        <v>0.02497239759799676</v>
       </c>
       <c r="W44">
-        <v>0.2297713064713065</v>
+        <v>0.2299115086463924</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1162135386053961</v>
+        <v>0.1135108981727126</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1571686632962984</v>
+        <v>0.1590686632962984</v>
       </c>
       <c r="C45">
-        <v>-14.1498205309382</v>
+        <v>-15.77913694053879</v>
       </c>
       <c r="D45">
-        <v>28.9321794690618</v>
+        <v>28.44686305946121</v>
       </c>
       <c r="E45">
-        <v>8.591999999999999</v>
+        <v>9.736000000000004</v>
       </c>
       <c r="F45">
-        <v>49.192</v>
+        <v>50.33600000000001</v>
       </c>
       <c r="G45">
         <v>6.11</v>
@@ -4965,37 +4965,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M45">
-        <v>11.5994736</v>
+        <v>11.8692288</v>
       </c>
       <c r="N45">
-        <v>-10.28280693333333</v>
+        <v>-10.55256213333334</v>
       </c>
       <c r="O45">
-        <v>-2.262217525333333</v>
+        <v>-2.321563669333334</v>
       </c>
       <c r="P45">
-        <v>-8.020589407999999</v>
+        <v>-8.230998464000002</v>
       </c>
       <c r="Q45">
-        <v>-3.420589408</v>
+        <v>-3.630998464000003</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1022924817164029</v>
+        <v>0.1033012760327673</v>
       </c>
       <c r="T45">
-        <v>1.304676252110923</v>
+        <v>1.327974042327189</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02497239759799676</v>
+        <v>0.02440484310713319</v>
       </c>
       <c r="W45">
-        <v>0.2299115086463924</v>
+        <v>0.230045337995338</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1135108981727126</v>
+        <v>0.1109311050324235</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1590686632962984</v>
+        <v>0.1609686632962984</v>
       </c>
       <c r="C46">
-        <v>-15.77913694053879</v>
+        <v>-17.39244029325656</v>
       </c>
       <c r="D46">
-        <v>28.44686305946121</v>
+        <v>27.97755970674344</v>
       </c>
       <c r="E46">
-        <v>9.736000000000004</v>
+        <v>10.88</v>
       </c>
       <c r="F46">
-        <v>50.33600000000001</v>
+        <v>51.48</v>
       </c>
       <c r="G46">
         <v>6.11</v>
@@ -5047,37 +5047,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M46">
-        <v>11.8692288</v>
+        <v>12.138984</v>
       </c>
       <c r="N46">
-        <v>-10.55256213333334</v>
+        <v>-10.82231733333333</v>
       </c>
       <c r="O46">
-        <v>-2.321563669333334</v>
+        <v>-2.380909813333334</v>
       </c>
       <c r="P46">
-        <v>-8.230998464000002</v>
+        <v>-8.44140752</v>
       </c>
       <c r="Q46">
-        <v>-3.630998464000003</v>
+        <v>-3.841407520000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1033012760327673</v>
+        <v>0.1043467537788176</v>
       </c>
       <c r="T46">
-        <v>1.327974042327189</v>
+        <v>1.352119024914956</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02440484310713319</v>
+        <v>0.02386251326030801</v>
       </c>
       <c r="W46">
-        <v>0.230045337995338</v>
+        <v>0.2301732193732194</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1109311050324235</v>
+        <v>0.1084659693650364</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1609686632962984</v>
+        <v>0.1628686632962984</v>
       </c>
       <c r="C47">
-        <v>-17.39244029325656</v>
+        <v>-18.99051025481641</v>
       </c>
       <c r="D47">
-        <v>27.97755970674344</v>
+        <v>27.5234897451836</v>
       </c>
       <c r="E47">
-        <v>10.88</v>
+        <v>12.024</v>
       </c>
       <c r="F47">
-        <v>51.48</v>
+        <v>52.624</v>
       </c>
       <c r="G47">
         <v>6.11</v>
@@ -5129,37 +5129,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M47">
-        <v>12.138984</v>
+        <v>12.4087392</v>
       </c>
       <c r="N47">
-        <v>-10.82231733333333</v>
+        <v>-11.09207253333333</v>
       </c>
       <c r="O47">
-        <v>-2.380909813333334</v>
+        <v>-2.440255957333333</v>
       </c>
       <c r="P47">
-        <v>-8.44140752</v>
+        <v>-8.651816576</v>
       </c>
       <c r="Q47">
-        <v>-3.841407520000001</v>
+        <v>-4.051816576</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1043467537788176</v>
+        <v>0.1054309529228698</v>
       </c>
       <c r="T47">
-        <v>1.352119024914956</v>
+        <v>1.377158266117085</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02386251326030801</v>
+        <v>0.02334376297204045</v>
       </c>
       <c r="W47">
-        <v>0.2301732193732194</v>
+        <v>0.2302955406911929</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1084659693650364</v>
+        <v>0.1061080135092748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1628686632962984</v>
+        <v>0.1647686632962984</v>
       </c>
       <c r="C48">
-        <v>-18.99051025481641</v>
+        <v>-20.57407668405002</v>
       </c>
       <c r="D48">
-        <v>27.5234897451836</v>
+        <v>27.08392331594999</v>
       </c>
       <c r="E48">
-        <v>12.024</v>
+        <v>13.16800000000001</v>
       </c>
       <c r="F48">
-        <v>52.624</v>
+        <v>53.76800000000001</v>
       </c>
       <c r="G48">
         <v>6.11</v>
@@ -5211,37 +5211,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M48">
-        <v>12.4087392</v>
+        <v>12.6784944</v>
       </c>
       <c r="N48">
-        <v>-11.09207253333333</v>
+        <v>-11.36182773333334</v>
       </c>
       <c r="O48">
-        <v>-2.440255957333333</v>
+        <v>-2.499602101333334</v>
       </c>
       <c r="P48">
-        <v>-8.651816576</v>
+        <v>-8.862225632000001</v>
       </c>
       <c r="Q48">
-        <v>-4.051816576</v>
+        <v>-4.262225632000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1054309529228698</v>
+        <v>0.1065560652421692</v>
       </c>
       <c r="T48">
-        <v>1.377158266117085</v>
+        <v>1.403142384345709</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02334376297204045</v>
+        <v>0.02284708716412469</v>
       </c>
       <c r="W48">
-        <v>0.2302955406911929</v>
+        <v>0.2304126568466994</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1061080135092748</v>
+        <v>0.1038503962005667</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1647686632962984</v>
+        <v>0.1666686632962984</v>
       </c>
       <c r="C49">
-        <v>-20.57407668405002</v>
+        <v>-22.14382354760352</v>
       </c>
       <c r="D49">
-        <v>27.08392331594999</v>
+        <v>26.65817645239648</v>
       </c>
       <c r="E49">
-        <v>13.16800000000001</v>
+        <v>14.312</v>
       </c>
       <c r="F49">
-        <v>53.76800000000001</v>
+        <v>54.91200000000001</v>
       </c>
       <c r="G49">
         <v>6.11</v>
@@ -5293,37 +5293,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M49">
-        <v>12.6784944</v>
+        <v>12.9482496</v>
       </c>
       <c r="N49">
-        <v>-11.36182773333334</v>
+        <v>-11.63158293333333</v>
       </c>
       <c r="O49">
-        <v>-2.499602101333334</v>
+        <v>-2.558948245333334</v>
       </c>
       <c r="P49">
-        <v>-8.862225632000001</v>
+        <v>-9.072634688000001</v>
       </c>
       <c r="Q49">
-        <v>-4.262225632000002</v>
+        <v>-4.472634688000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1065560652421692</v>
+        <v>0.1077244511122109</v>
       </c>
       <c r="T49">
-        <v>1.403142384345709</v>
+        <v>1.430125891736973</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02284708716412469</v>
+        <v>0.02237110618153876</v>
       </c>
       <c r="W49">
-        <v>0.2304126568466994</v>
+        <v>0.2305248931623932</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1038503962005667</v>
+        <v>0.1016868462797217</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1666686632962984</v>
+        <v>0.1685686632962984</v>
       </c>
       <c r="C50">
-        <v>-22.14382354760352</v>
+        <v>-23.700392471135</v>
       </c>
       <c r="D50">
-        <v>26.65817645239648</v>
+        <v>26.245607528865</v>
       </c>
       <c r="E50">
-        <v>14.312</v>
+        <v>15.456</v>
       </c>
       <c r="F50">
-        <v>54.912</v>
+        <v>56.056</v>
       </c>
       <c r="G50">
         <v>6.11</v>
@@ -5375,37 +5375,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M50">
-        <v>12.9482496</v>
+        <v>13.2180048</v>
       </c>
       <c r="N50">
-        <v>-11.63158293333333</v>
+        <v>-11.90133813333333</v>
       </c>
       <c r="O50">
-        <v>-2.558948245333334</v>
+        <v>-2.618294389333333</v>
       </c>
       <c r="P50">
-        <v>-9.072634688000001</v>
+        <v>-9.283043744</v>
       </c>
       <c r="Q50">
-        <v>-4.472634688000001</v>
+        <v>-4.683043744000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1077244511122109</v>
+        <v>0.1089386560359797</v>
       </c>
       <c r="T50">
-        <v>1.430125891736973</v>
+        <v>1.458167575888678</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02237110618153876</v>
+        <v>0.02191455299416042</v>
       </c>
       <c r="W50">
-        <v>0.2305248931623932</v>
+        <v>0.230632548403977</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1016868462797216</v>
+        <v>0.09961160451891105</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1685686632962984</v>
+        <v>0.1704686632962984</v>
       </c>
       <c r="C51">
-        <v>-23.700392471135</v>
+        <v>-25.2443859657819</v>
       </c>
       <c r="D51">
-        <v>26.245607528865</v>
+        <v>25.84561403421811</v>
       </c>
       <c r="E51">
-        <v>15.456</v>
+        <v>16.6</v>
       </c>
       <c r="F51">
-        <v>56.056</v>
+        <v>57.2</v>
       </c>
       <c r="G51">
         <v>6.11</v>
@@ -5457,37 +5457,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M51">
-        <v>13.2180048</v>
+        <v>13.48776</v>
       </c>
       <c r="N51">
-        <v>-11.90133813333333</v>
+        <v>-12.17109333333334</v>
       </c>
       <c r="O51">
-        <v>-2.618294389333333</v>
+        <v>-2.677640533333334</v>
       </c>
       <c r="P51">
-        <v>-9.283043744</v>
+        <v>-9.493452800000002</v>
       </c>
       <c r="Q51">
-        <v>-4.683043744000001</v>
+        <v>-4.893452800000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1089386560359797</v>
+        <v>0.1102014291566994</v>
       </c>
       <c r="T51">
-        <v>1.458167575888678</v>
+        <v>1.487330927406452</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02191455299416042</v>
+        <v>0.02147626193427721</v>
       </c>
       <c r="W51">
-        <v>0.230632548403977</v>
+        <v>0.2307358974358975</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.09961160451891105</v>
+        <v>0.09761937242853269</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1704686632962984</v>
+        <v>0.1723686632962984</v>
       </c>
       <c r="C52">
-        <v>-25.2443859657819</v>
+        <v>-26.77637036402158</v>
       </c>
       <c r="D52">
-        <v>25.84561403421811</v>
+        <v>25.45762963597842</v>
       </c>
       <c r="E52">
-        <v>16.6</v>
+        <v>17.744</v>
       </c>
       <c r="F52">
-        <v>57.2</v>
+        <v>58.344</v>
       </c>
       <c r="G52">
         <v>6.11</v>
@@ -5539,37 +5539,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M52">
-        <v>13.48776</v>
+        <v>13.7575152</v>
       </c>
       <c r="N52">
-        <v>-12.17109333333334</v>
+        <v>-12.44084853333333</v>
       </c>
       <c r="O52">
-        <v>-2.677640533333334</v>
+        <v>-2.736986677333333</v>
       </c>
       <c r="P52">
-        <v>-9.493452800000002</v>
+        <v>-9.703861856</v>
       </c>
       <c r="Q52">
-        <v>-4.893452800000002</v>
+        <v>-5.103861856</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1102014291566994</v>
+        <v>0.1115157440374483</v>
       </c>
       <c r="T52">
-        <v>1.487330927406452</v>
+        <v>1.517684619802502</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02147626193427721</v>
+        <v>0.0210551587590953</v>
       </c>
       <c r="W52">
-        <v>0.2307358974358975</v>
+        <v>0.2308351935646054</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.09761937242853269</v>
+        <v>0.09570526708679683</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1723686632962984</v>
+        <v>0.1742686632962984</v>
       </c>
       <c r="C53">
-        <v>-26.77637036402158</v>
+        <v>-28.29687849501069</v>
       </c>
       <c r="D53">
-        <v>25.45762963597842</v>
+        <v>25.08112150498932</v>
       </c>
       <c r="E53">
-        <v>17.744</v>
+        <v>18.88800000000001</v>
       </c>
       <c r="F53">
-        <v>58.344</v>
+        <v>59.48800000000001</v>
       </c>
       <c r="G53">
         <v>6.11</v>
@@ -5621,37 +5621,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M53">
-        <v>13.7575152</v>
+        <v>14.0272704</v>
       </c>
       <c r="N53">
-        <v>-12.44084853333333</v>
+        <v>-12.71060373333334</v>
       </c>
       <c r="O53">
-        <v>-2.736986677333333</v>
+        <v>-2.796332821333334</v>
       </c>
       <c r="P53">
-        <v>-9.703861856</v>
+        <v>-9.914270912000003</v>
       </c>
       <c r="Q53">
-        <v>-5.103861856</v>
+        <v>-5.314270912000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1115157440374483</v>
+        <v>0.1128848220382285</v>
       </c>
       <c r="T53">
-        <v>1.517684619802502</v>
+        <v>1.549303049381721</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0210551587590953</v>
+        <v>0.02065025185988193</v>
       </c>
       <c r="W53">
-        <v>0.2308351935646054</v>
+        <v>0.2309306706114398</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.09570526708679683</v>
+        <v>0.09386478118128139</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1742686632962984</v>
+        <v>0.1761686632962984</v>
       </c>
       <c r="C54">
-        <v>-28.29687849501069</v>
+        <v>-29.8064121259813</v>
       </c>
       <c r="D54">
-        <v>25.08112150498932</v>
+        <v>24.71558787401871</v>
       </c>
       <c r="E54">
-        <v>18.88800000000001</v>
+        <v>20.032</v>
       </c>
       <c r="F54">
-        <v>59.48800000000001</v>
+        <v>60.63200000000001</v>
       </c>
       <c r="G54">
         <v>6.11</v>
@@ -5703,37 +5703,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M54">
-        <v>14.0272704</v>
+        <v>14.2970256</v>
       </c>
       <c r="N54">
-        <v>-12.71060373333334</v>
+        <v>-12.98035893333333</v>
       </c>
       <c r="O54">
-        <v>-2.796332821333334</v>
+        <v>-2.855678965333334</v>
       </c>
       <c r="P54">
-        <v>-9.914270912000003</v>
+        <v>-10.124679968</v>
       </c>
       <c r="Q54">
-        <v>-5.314270912000003</v>
+        <v>-5.524679968000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1128848220382285</v>
+        <v>0.1143121586773397</v>
       </c>
       <c r="T54">
-        <v>1.549303049381721</v>
+        <v>1.582266944049417</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02065025185988193</v>
+        <v>0.02026062446629925</v>
       </c>
       <c r="W54">
-        <v>0.2309306706114398</v>
+        <v>0.2310225447508466</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.09386478118128139</v>
+        <v>0.0920937475740875</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1761686632962984</v>
+        <v>0.1780686632962984</v>
       </c>
       <c r="C55">
-        <v>-29.8064121259813</v>
+        <v>-31.30544419321737</v>
       </c>
       <c r="D55">
-        <v>24.71558787401871</v>
+        <v>24.36055580678265</v>
       </c>
       <c r="E55">
-        <v>20.032</v>
+        <v>21.17600000000001</v>
       </c>
       <c r="F55">
-        <v>60.63200000000001</v>
+        <v>61.77600000000001</v>
       </c>
       <c r="G55">
         <v>6.11</v>
@@ -5785,37 +5785,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M55">
-        <v>14.2970256</v>
+        <v>14.5667808</v>
       </c>
       <c r="N55">
-        <v>-12.98035893333333</v>
+        <v>-13.25011413333334</v>
       </c>
       <c r="O55">
-        <v>-2.855678965333334</v>
+        <v>-2.915025109333334</v>
       </c>
       <c r="P55">
-        <v>-10.124679968</v>
+        <v>-10.335089024</v>
       </c>
       <c r="Q55">
-        <v>-5.524679968000001</v>
+        <v>-5.735089024000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1143121586773397</v>
+        <v>0.1158015534311949</v>
       </c>
       <c r="T55">
-        <v>1.582266944049417</v>
+        <v>1.616664051528752</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02026062446629925</v>
+        <v>0.01988542771692334</v>
       </c>
       <c r="W55">
-        <v>0.2310225447508466</v>
+        <v>0.2311110161443495</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.0920937475740875</v>
+        <v>0.09038830780419693</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1780686632962984</v>
+        <v>0.1799686632962984</v>
       </c>
       <c r="C56">
-        <v>-31.30544419321737</v>
+        <v>-32.79442084347042</v>
       </c>
       <c r="D56">
-        <v>24.36055580678265</v>
+        <v>24.01557915652959</v>
       </c>
       <c r="E56">
-        <v>21.17600000000001</v>
+        <v>22.32000000000001</v>
       </c>
       <c r="F56">
-        <v>61.77600000000001</v>
+        <v>62.92000000000001</v>
       </c>
       <c r="G56">
         <v>6.11</v>
@@ -5867,37 +5867,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M56">
-        <v>14.5667808</v>
+        <v>14.836536</v>
       </c>
       <c r="N56">
-        <v>-13.25011413333334</v>
+        <v>-13.51986933333334</v>
       </c>
       <c r="O56">
-        <v>-2.915025109333334</v>
+        <v>-2.974371253333334</v>
       </c>
       <c r="P56">
-        <v>-10.335089024</v>
+        <v>-10.54549808</v>
       </c>
       <c r="Q56">
-        <v>-5.735089024000002</v>
+        <v>-5.945498080000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1158015534311949</v>
+        <v>0.1173571435074437</v>
       </c>
       <c r="T56">
-        <v>1.616664051528752</v>
+        <v>1.652589919340502</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01988542771692334</v>
+        <v>0.01952387448570655</v>
       </c>
       <c r="W56">
-        <v>0.2311110161443495</v>
+        <v>0.2311962703962704</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.09038830780419693</v>
+        <v>0.08874488402593883</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1799686632962984</v>
+        <v>0.1818686632962984</v>
       </c>
       <c r="C57">
-        <v>-32.79442084347042</v>
+        <v>-34.27376330434286</v>
       </c>
       <c r="D57">
-        <v>24.01557915652959</v>
+        <v>23.68023669565714</v>
       </c>
       <c r="E57">
-        <v>22.32000000000001</v>
+        <v>23.46400000000001</v>
       </c>
       <c r="F57">
-        <v>62.92000000000001</v>
+        <v>64.06400000000001</v>
       </c>
       <c r="G57">
         <v>6.11</v>
@@ -5949,37 +5949,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M57">
-        <v>14.836536</v>
+        <v>15.1062912</v>
       </c>
       <c r="N57">
-        <v>-13.51986933333334</v>
+        <v>-13.78962453333333</v>
       </c>
       <c r="O57">
-        <v>-2.974371253333334</v>
+        <v>-3.033717397333334</v>
       </c>
       <c r="P57">
-        <v>-10.54549808</v>
+        <v>-10.755907136</v>
       </c>
       <c r="Q57">
-        <v>-5.945498080000002</v>
+        <v>-6.155907136000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1173571435074437</v>
+        <v>0.118983442223522</v>
       </c>
       <c r="T57">
-        <v>1.652589919340502</v>
+        <v>1.690148781143695</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01952387448570655</v>
+        <v>0.01917523386989036</v>
       </c>
       <c r="W57">
-        <v>0.2311962703962704</v>
+        <v>0.2312784798534799</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.08874488402593883</v>
+        <v>0.08716015395404719</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1818686632962984</v>
+        <v>0.1837686632962984</v>
       </c>
       <c r="C58">
-        <v>-34.27376330434286</v>
+        <v>-35.74386960012632</v>
       </c>
       <c r="D58">
-        <v>23.68023669565714</v>
+        <v>23.3541303998737</v>
       </c>
       <c r="E58">
-        <v>23.46400000000001</v>
+        <v>24.60800000000001</v>
       </c>
       <c r="F58">
-        <v>64.06400000000001</v>
+        <v>65.20800000000001</v>
       </c>
       <c r="G58">
         <v>6.11</v>
@@ -6031,37 +6031,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M58">
-        <v>15.1062912</v>
+        <v>15.3760464</v>
       </c>
       <c r="N58">
-        <v>-13.78962453333333</v>
+        <v>-14.05937973333334</v>
       </c>
       <c r="O58">
-        <v>-3.033717397333334</v>
+        <v>-3.093063541333334</v>
       </c>
       <c r="P58">
-        <v>-10.755907136</v>
+        <v>-10.966316192</v>
       </c>
       <c r="Q58">
-        <v>-6.155907136000002</v>
+        <v>-6.366316192000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.118983442223522</v>
+        <v>0.1206853827403481</v>
       </c>
       <c r="T58">
-        <v>1.690148781143695</v>
+        <v>1.729454566751688</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01917523386989036</v>
+        <v>0.0188388262581379</v>
       </c>
       <c r="W58">
-        <v>0.2312784798534799</v>
+        <v>0.2313578047683311</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.08716015395404719</v>
+        <v>0.08563102844608128</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1837686632962984</v>
+        <v>0.1856686632962984</v>
       </c>
       <c r="C59">
-        <v>-35.74386960012632</v>
+        <v>-37.20511612779035</v>
       </c>
       <c r="D59">
-        <v>23.3541303998737</v>
+        <v>23.03688387220966</v>
       </c>
       <c r="E59">
-        <v>24.60800000000001</v>
+        <v>25.75200000000002</v>
       </c>
       <c r="F59">
-        <v>65.20800000000001</v>
+        <v>66.35200000000002</v>
       </c>
       <c r="G59">
         <v>6.11</v>
@@ -6113,37 +6113,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M59">
-        <v>15.3760464</v>
+        <v>15.64580160000001</v>
       </c>
       <c r="N59">
-        <v>-14.05937973333334</v>
+        <v>-14.32913493333334</v>
       </c>
       <c r="O59">
-        <v>-3.093063541333334</v>
+        <v>-3.152409685333335</v>
       </c>
       <c r="P59">
-        <v>-10.966316192</v>
+        <v>-11.176725248</v>
       </c>
       <c r="Q59">
-        <v>-6.366316192000003</v>
+        <v>-6.576725248000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1206853827403481</v>
+        <v>0.1224683680436897</v>
       </c>
       <c r="T59">
-        <v>1.729454566751688</v>
+        <v>1.770632056436252</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0188388262581379</v>
+        <v>0.01851401890885966</v>
       </c>
       <c r="W59">
-        <v>0.2313578047683311</v>
+        <v>0.2314343943412909</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.08563102844608128</v>
+        <v>0.08415463140390744</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1856686632962984</v>
+        <v>0.1875686632962984</v>
       </c>
       <c r="C60">
-        <v>-37.20511612779034</v>
+        <v>-38.6578591062419</v>
       </c>
       <c r="D60">
-        <v>23.03688387220966</v>
+        <v>22.72814089375809</v>
       </c>
       <c r="E60">
-        <v>25.752</v>
+        <v>26.89599999999999</v>
       </c>
       <c r="F60">
-        <v>66.352</v>
+        <v>67.496</v>
       </c>
       <c r="G60">
         <v>6.11</v>
@@ -6195,37 +6195,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M60">
-        <v>15.6458016</v>
+        <v>15.9155568</v>
       </c>
       <c r="N60">
-        <v>-14.32913493333334</v>
+        <v>-14.59889013333333</v>
       </c>
       <c r="O60">
-        <v>-3.152409685333334</v>
+        <v>-3.211755829333333</v>
       </c>
       <c r="P60">
-        <v>-11.176725248</v>
+        <v>-11.387134304</v>
       </c>
       <c r="Q60">
-        <v>-6.576725248000002</v>
+        <v>-6.787134303999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1224683680436897</v>
+        <v>0.1243383282398773</v>
       </c>
       <c r="T60">
-        <v>1.770632056436252</v>
+        <v>1.813818204154209</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01851401890885966</v>
+        <v>0.01820022197820103</v>
       </c>
       <c r="W60">
-        <v>0.2314343943412909</v>
+        <v>0.2315083876575402</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.08415463140390755</v>
+        <v>0.08272828171909563</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1875686632962984</v>
+        <v>0.1894686632962984</v>
       </c>
       <c r="C61">
-        <v>-38.6578591062419</v>
+        <v>-40.10243591058706</v>
       </c>
       <c r="D61">
-        <v>22.72814089375809</v>
+        <v>22.42756408941294</v>
       </c>
       <c r="E61">
-        <v>26.89599999999999</v>
+        <v>28.04</v>
       </c>
       <c r="F61">
-        <v>67.496</v>
+        <v>68.64</v>
       </c>
       <c r="G61">
         <v>6.11</v>
@@ -6277,37 +6277,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M61">
-        <v>15.9155568</v>
+        <v>16.185312</v>
       </c>
       <c r="N61">
-        <v>-14.59889013333333</v>
+        <v>-14.86864533333333</v>
       </c>
       <c r="O61">
-        <v>-3.211755829333333</v>
+        <v>-3.271101973333333</v>
       </c>
       <c r="P61">
-        <v>-11.387134304</v>
+        <v>-11.59754336</v>
       </c>
       <c r="Q61">
-        <v>-6.787134303999999</v>
+        <v>-6.99754336</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1243383282398773</v>
+        <v>0.1263017864458742</v>
       </c>
       <c r="T61">
-        <v>1.813818204154209</v>
+        <v>1.859163659258065</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01820022197820103</v>
+        <v>0.01789688494523101</v>
       </c>
       <c r="W61">
-        <v>0.2315083876575402</v>
+        <v>0.2315799145299145</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.08272828171909563</v>
+        <v>0.08134947702377726</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1894686632962984</v>
+        <v>0.1913686632962984</v>
       </c>
       <c r="C62">
-        <v>-40.10243591058706</v>
+        <v>-41.53916630190177</v>
       </c>
       <c r="D62">
-        <v>22.42756408941294</v>
+        <v>22.13483369809823</v>
       </c>
       <c r="E62">
-        <v>28.04</v>
+        <v>29.184</v>
       </c>
       <c r="F62">
-        <v>68.64</v>
+        <v>69.78400000000001</v>
       </c>
       <c r="G62">
         <v>6.11</v>
@@ -6359,37 +6359,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M62">
-        <v>16.185312</v>
+        <v>16.4550672</v>
       </c>
       <c r="N62">
-        <v>-14.86864533333333</v>
+        <v>-15.13840053333334</v>
       </c>
       <c r="O62">
-        <v>-3.271101973333333</v>
+        <v>-3.330448117333334</v>
       </c>
       <c r="P62">
-        <v>-11.59754336</v>
+        <v>-11.807952416</v>
       </c>
       <c r="Q62">
-        <v>-6.99754336</v>
+        <v>-7.207952416000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1263017864458742</v>
+        <v>0.1283659348162812</v>
       </c>
       <c r="T62">
-        <v>1.859163659258065</v>
+        <v>1.906834522315964</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01789688494523101</v>
+        <v>0.01760349338875181</v>
       </c>
       <c r="W62">
-        <v>0.2315799145299145</v>
+        <v>0.2316490962589323</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.08134947702377726</v>
+        <v>0.08001587903978091</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1913686632962984</v>
+        <v>0.1932686632962984</v>
       </c>
       <c r="C63">
-        <v>-41.53916630190177</v>
+        <v>-42.96835356193603</v>
       </c>
       <c r="D63">
-        <v>22.13483369809823</v>
+        <v>21.84964643806396</v>
       </c>
       <c r="E63">
-        <v>29.184</v>
+        <v>30.328</v>
       </c>
       <c r="F63">
-        <v>69.78400000000001</v>
+        <v>70.928</v>
       </c>
       <c r="G63">
         <v>6.11</v>
@@ -6441,37 +6441,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M63">
-        <v>16.4550672</v>
+        <v>16.7248224</v>
       </c>
       <c r="N63">
-        <v>-15.13840053333334</v>
+        <v>-15.40815573333333</v>
       </c>
       <c r="O63">
-        <v>-3.330448117333334</v>
+        <v>-3.389794261333333</v>
       </c>
       <c r="P63">
-        <v>-11.807952416</v>
+        <v>-12.018361472</v>
       </c>
       <c r="Q63">
-        <v>-7.207952416000003</v>
+        <v>-7.418361472000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1283659348162812</v>
+        <v>0.1305387225746044</v>
       </c>
       <c r="T63">
-        <v>1.906834522315964</v>
+        <v>1.957014378166384</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01760349338875181</v>
+        <v>0.01731956607603001</v>
       </c>
       <c r="W63">
-        <v>0.2316490962589323</v>
+        <v>0.2317160463192721</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.08001587903978091</v>
+        <v>0.07872530034559089</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1932686632962984</v>
+        <v>0.1951686632962984</v>
       </c>
       <c r="C64">
-        <v>-42.96835356193603</v>
+        <v>-44.39028554121586</v>
       </c>
       <c r="D64">
-        <v>21.84964643806396</v>
+        <v>21.57171445878415</v>
       </c>
       <c r="E64">
-        <v>30.328</v>
+        <v>31.472</v>
       </c>
       <c r="F64">
-        <v>70.928</v>
+        <v>72.072</v>
       </c>
       <c r="G64">
         <v>6.11</v>
@@ -6523,37 +6523,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M64">
-        <v>16.7248224</v>
+        <v>16.9945776</v>
       </c>
       <c r="N64">
-        <v>-15.40815573333333</v>
+        <v>-15.67791093333334</v>
       </c>
       <c r="O64">
-        <v>-3.389794261333333</v>
+        <v>-3.449140405333334</v>
       </c>
       <c r="P64">
-        <v>-12.018361472</v>
+        <v>-12.228770528</v>
       </c>
       <c r="Q64">
-        <v>-7.418361472000001</v>
+        <v>-7.628770528000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1305387225746044</v>
+        <v>0.132828958319864</v>
       </c>
       <c r="T64">
-        <v>1.957014378166384</v>
+        <v>2.009906658657367</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01731956607603001</v>
+        <v>0.01704465232879144</v>
       </c>
       <c r="W64">
-        <v>0.2317160463192721</v>
+        <v>0.231780870980871</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.07872530034559089</v>
+        <v>0.07747569240359742</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1951686632962984</v>
+        <v>0.1970686632962984</v>
       </c>
       <c r="C65">
-        <v>-44.39028554121586</v>
+        <v>-45.80523562815758</v>
       </c>
       <c r="D65">
-        <v>21.57171445878415</v>
+        <v>21.30076437184243</v>
       </c>
       <c r="E65">
-        <v>31.472</v>
+        <v>32.61600000000001</v>
       </c>
       <c r="F65">
-        <v>72.072</v>
+        <v>73.21600000000001</v>
       </c>
       <c r="G65">
         <v>6.11</v>
@@ -6605,37 +6605,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M65">
-        <v>16.9945776</v>
+        <v>17.2643328</v>
       </c>
       <c r="N65">
-        <v>-15.67791093333334</v>
+        <v>-15.94766613333334</v>
       </c>
       <c r="O65">
-        <v>-3.449140405333334</v>
+        <v>-3.508486549333334</v>
       </c>
       <c r="P65">
-        <v>-12.228770528</v>
+        <v>-12.439179584</v>
       </c>
       <c r="Q65">
-        <v>-7.628770528000002</v>
+        <v>-7.839179584000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.132828958319864</v>
+        <v>0.1352464293843046</v>
       </c>
       <c r="T65">
-        <v>2.009906658657367</v>
+        <v>2.065737399175627</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01704465232879144</v>
+        <v>0.01677832963615407</v>
       </c>
       <c r="W65">
-        <v>0.231780870980871</v>
+        <v>0.2318436698717949</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.07747569240359742</v>
+        <v>0.07626513470979113</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1970686632962984</v>
+        <v>0.1989686632962984</v>
       </c>
       <c r="C66">
-        <v>-45.80523562815758</v>
+        <v>-47.21346364605319</v>
       </c>
       <c r="D66">
-        <v>21.30076437184243</v>
+        <v>21.03653635394681</v>
       </c>
       <c r="E66">
-        <v>32.61600000000001</v>
+        <v>33.76</v>
       </c>
       <c r="F66">
-        <v>73.21600000000001</v>
+        <v>74.36</v>
       </c>
       <c r="G66">
         <v>6.11</v>
@@ -6687,37 +6687,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M66">
-        <v>17.2643328</v>
+        <v>17.534088</v>
       </c>
       <c r="N66">
-        <v>-15.94766613333334</v>
+        <v>-16.21742133333333</v>
       </c>
       <c r="O66">
-        <v>-3.508486549333334</v>
+        <v>-3.567832693333334</v>
       </c>
       <c r="P66">
-        <v>-12.439179584</v>
+        <v>-12.64958864</v>
       </c>
       <c r="Q66">
-        <v>-7.839179584000002</v>
+        <v>-8.049588640000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1352464293843046</v>
+        <v>0.1378020416524277</v>
       </c>
       <c r="T66">
-        <v>2.065737399175627</v>
+        <v>2.124758467723503</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01677832963615407</v>
+        <v>0.01652020148790555</v>
       </c>
       <c r="W66">
-        <v>0.2318436698717949</v>
+        <v>0.2319045364891519</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.07626513470979113</v>
+        <v>0.0750918249450252</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1989686632962984</v>
+        <v>0.2008686632962984</v>
       </c>
       <c r="C67">
-        <v>-47.21346364605319</v>
+        <v>-48.61521668411301</v>
       </c>
       <c r="D67">
-        <v>21.03653635394681</v>
+        <v>20.77878331588699</v>
       </c>
       <c r="E67">
-        <v>33.76</v>
+        <v>34.904</v>
       </c>
       <c r="F67">
-        <v>74.36</v>
+        <v>75.504</v>
       </c>
       <c r="G67">
         <v>6.11</v>
@@ -6769,37 +6769,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M67">
-        <v>17.534088</v>
+        <v>17.8038432</v>
       </c>
       <c r="N67">
-        <v>-16.21742133333333</v>
+        <v>-16.48717653333334</v>
       </c>
       <c r="O67">
-        <v>-3.567832693333334</v>
+        <v>-3.627178837333334</v>
       </c>
       <c r="P67">
-        <v>-12.64958864</v>
+        <v>-12.859997696</v>
       </c>
       <c r="Q67">
-        <v>-8.049588640000001</v>
+        <v>-8.259997696000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1378020416524277</v>
+        <v>0.1405079840539696</v>
       </c>
       <c r="T67">
-        <v>2.124758467723503</v>
+        <v>2.187251363833017</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01652020148790555</v>
+        <v>0.01626989540475546</v>
       </c>
       <c r="W67">
-        <v>0.2319045364891519</v>
+        <v>0.2319635586635587</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0750918249450252</v>
+        <v>0.07395407002161569</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2008686632962984</v>
+        <v>0.2027686632962984</v>
       </c>
       <c r="C68">
-        <v>-48.61521668411301</v>
+        <v>-50.01072986815322</v>
       </c>
       <c r="D68">
-        <v>20.77878331588699</v>
+        <v>20.52727013184679</v>
       </c>
       <c r="E68">
-        <v>34.904</v>
+        <v>36.04800000000001</v>
       </c>
       <c r="F68">
-        <v>75.504</v>
+        <v>76.64800000000001</v>
       </c>
       <c r="G68">
         <v>6.11</v>
@@ -6851,37 +6851,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M68">
-        <v>17.8038432</v>
+        <v>18.0735984</v>
       </c>
       <c r="N68">
-        <v>-16.48717653333334</v>
+        <v>-16.75693173333334</v>
       </c>
       <c r="O68">
-        <v>-3.627178837333334</v>
+        <v>-3.686524981333334</v>
       </c>
       <c r="P68">
-        <v>-12.859997696</v>
+        <v>-13.070406752</v>
       </c>
       <c r="Q68">
-        <v>-8.259997696000003</v>
+        <v>-8.470406752000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1405079840539696</v>
+        <v>0.143377922964696</v>
       </c>
       <c r="T68">
-        <v>2.187251363833017</v>
+        <v>2.253531708191594</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01626989540475546</v>
+        <v>0.01602706114498299</v>
       </c>
       <c r="W68">
-        <v>0.2319635586635587</v>
+        <v>0.232020818982013</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.07395407002161569</v>
+        <v>0.07285027793174081</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2027686632962984</v>
+        <v>0.2046686632962984</v>
       </c>
       <c r="C69">
-        <v>-50.01072986815322</v>
+        <v>-51.40022707598061</v>
       </c>
       <c r="D69">
-        <v>20.52727013184679</v>
+        <v>20.2817729240194</v>
       </c>
       <c r="E69">
-        <v>36.04800000000001</v>
+        <v>37.19200000000001</v>
       </c>
       <c r="F69">
-        <v>76.64800000000001</v>
+        <v>77.79200000000002</v>
       </c>
       <c r="G69">
         <v>6.11</v>
@@ -6933,37 +6933,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M69">
-        <v>18.0735984</v>
+        <v>18.3433536</v>
       </c>
       <c r="N69">
-        <v>-16.75693173333334</v>
+        <v>-17.02668693333334</v>
       </c>
       <c r="O69">
-        <v>-3.686524981333334</v>
+        <v>-3.745871125333334</v>
       </c>
       <c r="P69">
-        <v>-13.070406752</v>
+        <v>-13.280815808</v>
       </c>
       <c r="Q69">
-        <v>-8.470406752000002</v>
+        <v>-8.680815808000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.143377922964696</v>
+        <v>0.1464272330573428</v>
       </c>
       <c r="T69">
-        <v>2.253531708191594</v>
+        <v>2.323954574072581</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01602706114498299</v>
+        <v>0.01579136906932148</v>
       </c>
       <c r="W69">
-        <v>0.232020818982013</v>
+        <v>0.232076395173454</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.07285027793174081</v>
+        <v>0.07177895031509762</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2046686632962984</v>
+        <v>0.2065686632962984</v>
       </c>
       <c r="C70">
-        <v>-51.40022707598061</v>
+        <v>-52.78392160205013</v>
       </c>
       <c r="D70">
-        <v>20.2817729240194</v>
+        <v>20.04207839794988</v>
       </c>
       <c r="E70">
-        <v>37.19200000000001</v>
+        <v>38.33600000000001</v>
       </c>
       <c r="F70">
-        <v>77.79200000000002</v>
+        <v>78.93600000000001</v>
       </c>
       <c r="G70">
         <v>6.11</v>
@@ -7015,37 +7015,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M70">
-        <v>18.3433536</v>
+        <v>18.6131088</v>
       </c>
       <c r="N70">
-        <v>-17.02668693333334</v>
+        <v>-17.29644213333334</v>
       </c>
       <c r="O70">
-        <v>-3.745871125333334</v>
+        <v>-3.805217269333334</v>
       </c>
       <c r="P70">
-        <v>-13.280815808</v>
+        <v>-13.491224864</v>
       </c>
       <c r="Q70">
-        <v>-8.680815808000004</v>
+        <v>-8.891224864000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1464272330573428</v>
+        <v>0.1496732728333861</v>
       </c>
       <c r="T70">
-        <v>2.323954574072581</v>
+        <v>2.398920850655568</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01579136906932148</v>
+        <v>0.01556250864802696</v>
       </c>
       <c r="W70">
-        <v>0.232076395173454</v>
+        <v>0.2321303604607952</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.07177895031509762</v>
+        <v>0.07073867567284975</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2065686632962984</v>
+        <v>0.2084686632962984</v>
       </c>
       <c r="C71">
-        <v>-52.78392160205013</v>
+        <v>-54.1620167755424</v>
       </c>
       <c r="D71">
-        <v>20.04207839794988</v>
+        <v>19.80798322445761</v>
       </c>
       <c r="E71">
-        <v>38.33600000000001</v>
+        <v>39.48000000000001</v>
       </c>
       <c r="F71">
-        <v>78.93600000000001</v>
+        <v>80.08000000000001</v>
       </c>
       <c r="G71">
         <v>6.11</v>
@@ -7097,37 +7097,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M71">
-        <v>18.6131088</v>
+        <v>18.882864</v>
       </c>
       <c r="N71">
-        <v>-17.29644213333334</v>
+        <v>-17.56619733333334</v>
       </c>
       <c r="O71">
-        <v>-3.805217269333334</v>
+        <v>-3.864563413333335</v>
       </c>
       <c r="P71">
-        <v>-13.491224864</v>
+        <v>-13.70163392</v>
       </c>
       <c r="Q71">
-        <v>-8.891224864000003</v>
+        <v>-9.101633920000005</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1496732728333861</v>
+        <v>0.1531357152611656</v>
       </c>
       <c r="T71">
-        <v>2.398920850655568</v>
+        <v>2.478884879010753</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01556250864802696</v>
+        <v>0.01534018709591229</v>
       </c>
       <c r="W71">
-        <v>0.2321303604607952</v>
+        <v>0.2321827838827839</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.07073867567284975</v>
+        <v>0.06972812316323762</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2084686632962984</v>
+        <v>0.2103686632962984</v>
       </c>
       <c r="C72">
-        <v>-54.1620167755424</v>
+        <v>-55.53470653562577</v>
       </c>
       <c r="D72">
-        <v>19.80798322445761</v>
+        <v>19.57929346437425</v>
       </c>
       <c r="E72">
-        <v>39.48000000000001</v>
+        <v>40.62400000000002</v>
       </c>
       <c r="F72">
-        <v>80.08000000000001</v>
+        <v>81.22400000000002</v>
       </c>
       <c r="G72">
         <v>6.11</v>
@@ -7179,37 +7179,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M72">
-        <v>18.882864</v>
+        <v>19.1526192</v>
       </c>
       <c r="N72">
-        <v>-17.56619733333334</v>
+        <v>-17.83595253333334</v>
       </c>
       <c r="O72">
-        <v>-3.864563413333335</v>
+        <v>-3.923909557333334</v>
       </c>
       <c r="P72">
-        <v>-13.70163392</v>
+        <v>-13.912042976</v>
       </c>
       <c r="Q72">
-        <v>-9.101633920000005</v>
+        <v>-9.312042976000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1531357152611656</v>
+        <v>0.1568369468218955</v>
       </c>
       <c r="T72">
-        <v>2.478884879010753</v>
+        <v>2.564363667942159</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01534018709591229</v>
+        <v>0.01512412812273043</v>
       </c>
       <c r="W72">
-        <v>0.2321827838827839</v>
+        <v>0.2322337305886602</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.06972812316323762</v>
+        <v>0.06874603692150194</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2103686632962984</v>
+        <v>0.2122686632962984</v>
       </c>
       <c r="C73">
-        <v>-55.53470653562577</v>
+        <v>-56.90217596732352</v>
       </c>
       <c r="D73">
-        <v>19.57929346437423</v>
+        <v>19.35582403267648</v>
       </c>
       <c r="E73">
-        <v>40.624</v>
+        <v>41.76799999999999</v>
       </c>
       <c r="F73">
-        <v>81.224</v>
+        <v>82.36799999999999</v>
       </c>
       <c r="G73">
         <v>6.11</v>
@@ -7261,37 +7261,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M73">
-        <v>19.1526192</v>
+        <v>19.4223744</v>
       </c>
       <c r="N73">
-        <v>-17.83595253333333</v>
+        <v>-18.10570773333333</v>
       </c>
       <c r="O73">
-        <v>-3.923909557333333</v>
+        <v>-3.983255701333333</v>
       </c>
       <c r="P73">
-        <v>-13.912042976</v>
+        <v>-14.122452032</v>
       </c>
       <c r="Q73">
-        <v>-9.312042976000001</v>
+        <v>-9.522452032</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1568369468218954</v>
+        <v>0.1608025520655345</v>
       </c>
       <c r="T73">
-        <v>2.564363667942158</v>
+        <v>2.655948084654378</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01512412812273043</v>
+        <v>0.01491407078769251</v>
       </c>
       <c r="W73">
-        <v>0.2322337305886602</v>
+        <v>0.2322832621082621</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.06874603692150194</v>
+        <v>0.06779123085314775</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2122686632962984</v>
+        <v>0.2141686632962984</v>
       </c>
       <c r="C74">
-        <v>-56.90217596732352</v>
+        <v>-58.26460180109856</v>
       </c>
       <c r="D74">
-        <v>19.35582403267648</v>
+        <v>19.13739819890143</v>
       </c>
       <c r="E74">
-        <v>41.76799999999999</v>
+        <v>42.912</v>
       </c>
       <c r="F74">
-        <v>82.36799999999999</v>
+        <v>83.512</v>
       </c>
       <c r="G74">
         <v>6.11</v>
@@ -7343,37 +7343,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M74">
-        <v>19.4223744</v>
+        <v>19.6921296</v>
       </c>
       <c r="N74">
-        <v>-18.10570773333333</v>
+        <v>-18.37546293333333</v>
       </c>
       <c r="O74">
-        <v>-3.983255701333333</v>
+        <v>-4.042601845333333</v>
       </c>
       <c r="P74">
-        <v>-14.122452032</v>
+        <v>-14.332861088</v>
       </c>
       <c r="Q74">
-        <v>-9.522452032</v>
+        <v>-9.732861088000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1608025520655345</v>
+        <v>0.1650619058457395</v>
       </c>
       <c r="T74">
-        <v>2.655948084654378</v>
+        <v>2.754316532234169</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01491407078769251</v>
+        <v>0.01470976844813508</v>
       </c>
       <c r="W74">
-        <v>0.2322832621082621</v>
+        <v>0.2323314365999297</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.06779123085314775</v>
+        <v>0.06686258385515942</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2141686632962984</v>
+        <v>0.2160686632962984</v>
       </c>
       <c r="C75">
-        <v>-58.26460180109856</v>
+        <v>-59.62215287898917</v>
       </c>
       <c r="D75">
-        <v>19.13739819890143</v>
+        <v>18.92384712101084</v>
       </c>
       <c r="E75">
-        <v>42.912</v>
+        <v>44.056</v>
       </c>
       <c r="F75">
-        <v>83.512</v>
+        <v>84.65600000000001</v>
       </c>
       <c r="G75">
         <v>6.11</v>
@@ -7425,37 +7425,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M75">
-        <v>19.6921296</v>
+        <v>19.9618848</v>
       </c>
       <c r="N75">
-        <v>-18.37546293333333</v>
+        <v>-18.64521813333334</v>
       </c>
       <c r="O75">
-        <v>-4.042601845333333</v>
+        <v>-4.101947989333334</v>
       </c>
       <c r="P75">
-        <v>-14.332861088</v>
+        <v>-14.543270144</v>
       </c>
       <c r="Q75">
-        <v>-9.732861088000002</v>
+        <v>-9.943270144000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1650619058457395</v>
+        <v>0.1696489022244218</v>
       </c>
       <c r="T75">
-        <v>2.754316532234169</v>
+        <v>2.860251783473945</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01470976844813508</v>
+        <v>0.01451098779343055</v>
       </c>
       <c r="W75">
-        <v>0.2323314365999297</v>
+        <v>0.2323783090783091</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.06686258385515942</v>
+        <v>0.06595903542468429</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2160686632962984</v>
+        <v>0.2179686632962984</v>
       </c>
       <c r="C76">
-        <v>-59.62215287898917</v>
+        <v>-60.97499058987992</v>
       </c>
       <c r="D76">
-        <v>18.92384712101084</v>
+        <v>18.71500941012009</v>
       </c>
       <c r="E76">
-        <v>44.056</v>
+        <v>45.20000000000001</v>
       </c>
       <c r="F76">
-        <v>84.65600000000001</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="G76">
         <v>6.11</v>
@@ -7507,37 +7507,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M76">
-        <v>19.9618848</v>
+        <v>20.23164</v>
       </c>
       <c r="N76">
-        <v>-18.64521813333334</v>
+        <v>-18.91497333333334</v>
       </c>
       <c r="O76">
-        <v>-4.101947989333334</v>
+        <v>-4.161294133333334</v>
       </c>
       <c r="P76">
-        <v>-14.543270144</v>
+        <v>-14.7536792</v>
       </c>
       <c r="Q76">
-        <v>-9.943270144000003</v>
+        <v>-10.1536792</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1696489022244218</v>
+        <v>0.1746028583133987</v>
       </c>
       <c r="T76">
-        <v>2.860251783473945</v>
+        <v>2.974661854812903</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01451098779343055</v>
+        <v>0.01431750795618481</v>
       </c>
       <c r="W76">
-        <v>0.2323783090783091</v>
+        <v>0.2324239316239316</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.06595903542468429</v>
+        <v>0.06507958161902183</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2179686632962984</v>
+        <v>0.2198686632962984</v>
       </c>
       <c r="C77">
-        <v>-60.97499058987992</v>
+        <v>-62.32326927626647</v>
       </c>
       <c r="D77">
-        <v>18.71500941012009</v>
+        <v>18.51073072373354</v>
       </c>
       <c r="E77">
-        <v>45.20000000000001</v>
+        <v>46.344</v>
       </c>
       <c r="F77">
-        <v>85.80000000000001</v>
+        <v>86.944</v>
       </c>
       <c r="G77">
         <v>6.11</v>
@@ -7589,37 +7589,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M77">
-        <v>20.23164</v>
+        <v>20.5013952</v>
       </c>
       <c r="N77">
-        <v>-18.91497333333334</v>
+        <v>-19.18472853333333</v>
       </c>
       <c r="O77">
-        <v>-4.161294133333334</v>
+        <v>-4.220640277333334</v>
       </c>
       <c r="P77">
-        <v>-14.7536792</v>
+        <v>-14.964088256</v>
       </c>
       <c r="Q77">
-        <v>-10.1536792</v>
+        <v>-10.364088256</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1746028583133987</v>
+        <v>0.179969644076457</v>
       </c>
       <c r="T77">
-        <v>2.974661854812903</v>
+        <v>3.098606098763441</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01431750795618481</v>
+        <v>0.01412911969360343</v>
       </c>
       <c r="W77">
-        <v>0.2324239316239316</v>
+        <v>0.2324683535762483</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.06507958161902183</v>
+        <v>0.06422327133456096</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2198686632962984</v>
+        <v>0.2217686632962984</v>
       </c>
       <c r="C78">
-        <v>-62.32326927626647</v>
+        <v>-63.66713661466792</v>
       </c>
       <c r="D78">
-        <v>18.51073072373354</v>
+        <v>18.31086338533208</v>
       </c>
       <c r="E78">
-        <v>46.344</v>
+        <v>47.48800000000001</v>
       </c>
       <c r="F78">
-        <v>86.944</v>
+        <v>88.08800000000001</v>
       </c>
       <c r="G78">
         <v>6.11</v>
@@ -7671,37 +7671,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M78">
-        <v>20.5013952</v>
+        <v>20.7711504</v>
       </c>
       <c r="N78">
-        <v>-19.18472853333333</v>
+        <v>-19.45448373333334</v>
       </c>
       <c r="O78">
-        <v>-4.220640277333334</v>
+        <v>-4.279986421333335</v>
       </c>
       <c r="P78">
-        <v>-14.964088256</v>
+        <v>-15.174497312</v>
       </c>
       <c r="Q78">
-        <v>-10.364088256</v>
+        <v>-10.574497312</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.179969644076457</v>
+        <v>0.1858031068623899</v>
       </c>
       <c r="T78">
-        <v>3.098606098763441</v>
+        <v>3.233328103057504</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01412911969360343</v>
+        <v>0.01394562463264754</v>
       </c>
       <c r="W78">
-        <v>0.2324683535762483</v>
+        <v>0.2325116217116217</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.06422327133456096</v>
+        <v>0.06338920287567062</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2217686632962984</v>
+        <v>0.2236686632962984</v>
       </c>
       <c r="C79">
-        <v>-63.66713661466792</v>
+        <v>-65.00673397165809</v>
       </c>
       <c r="D79">
-        <v>18.31086338533208</v>
+        <v>18.11526602834192</v>
       </c>
       <c r="E79">
-        <v>47.48800000000001</v>
+        <v>48.63200000000001</v>
       </c>
       <c r="F79">
-        <v>88.08800000000001</v>
+        <v>89.23200000000001</v>
       </c>
       <c r="G79">
         <v>6.11</v>
@@ -7753,37 +7753,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M79">
-        <v>20.7711504</v>
+        <v>21.04090560000001</v>
       </c>
       <c r="N79">
-        <v>-19.45448373333334</v>
+        <v>-19.72423893333334</v>
       </c>
       <c r="O79">
-        <v>-4.279986421333335</v>
+        <v>-4.339332565333335</v>
       </c>
       <c r="P79">
-        <v>-15.174497312</v>
+        <v>-15.384906368</v>
       </c>
       <c r="Q79">
-        <v>-10.574497312</v>
+        <v>-10.78490636800001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1858031068623899</v>
+        <v>0.192166884447044</v>
       </c>
       <c r="T79">
-        <v>3.233328103057504</v>
+        <v>3.38029756228739</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01394562463264754</v>
+        <v>0.01376683457325462</v>
       </c>
       <c r="W79">
-        <v>0.2325116217116217</v>
+        <v>0.2325537804076266</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.06338920287567062</v>
+        <v>0.06257652078752096</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2236686632962984</v>
+        <v>0.2255686632962984</v>
       </c>
       <c r="C80">
-        <v>-65.00673397165809</v>
+        <v>-66.34219673731886</v>
       </c>
       <c r="D80">
-        <v>18.11526602834192</v>
+        <v>17.92380326268115</v>
       </c>
       <c r="E80">
-        <v>48.63200000000001</v>
+        <v>49.776</v>
       </c>
       <c r="F80">
-        <v>89.23200000000001</v>
+        <v>90.376</v>
       </c>
       <c r="G80">
         <v>6.11</v>
@@ -7835,37 +7835,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M80">
-        <v>21.04090560000001</v>
+        <v>21.3106608</v>
       </c>
       <c r="N80">
-        <v>-19.72423893333334</v>
+        <v>-19.99399413333333</v>
       </c>
       <c r="O80">
-        <v>-4.339332565333335</v>
+        <v>-4.398678709333334</v>
       </c>
       <c r="P80">
-        <v>-15.384906368</v>
+        <v>-15.595315424</v>
       </c>
       <c r="Q80">
-        <v>-10.78490636800001</v>
+        <v>-10.995315424</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.192166884447044</v>
+        <v>0.1991367360873794</v>
       </c>
       <c r="T80">
-        <v>3.38029756228739</v>
+        <v>3.541264112872504</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01376683457325462</v>
+        <v>0.01359257084447925</v>
       </c>
       <c r="W80">
-        <v>0.2325537804076266</v>
+        <v>0.2325948717948718</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.06257652078752096</v>
+        <v>0.06178441292945114</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2255686632962984</v>
+        <v>0.2274686632962984</v>
       </c>
       <c r="C81">
-        <v>-66.34219673731886</v>
+        <v>-67.67365463776895</v>
       </c>
       <c r="D81">
-        <v>17.92380326268115</v>
+        <v>17.73634536223107</v>
       </c>
       <c r="E81">
-        <v>49.776</v>
+        <v>50.92000000000001</v>
       </c>
       <c r="F81">
-        <v>90.376</v>
+        <v>91.52000000000001</v>
       </c>
       <c r="G81">
         <v>6.11</v>
@@ -7917,37 +7917,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M81">
-        <v>21.3106608</v>
+        <v>21.580416</v>
       </c>
       <c r="N81">
-        <v>-19.99399413333333</v>
+        <v>-20.26374933333334</v>
       </c>
       <c r="O81">
-        <v>-4.398678709333334</v>
+        <v>-4.458024853333334</v>
       </c>
       <c r="P81">
-        <v>-15.595315424</v>
+        <v>-15.80572448</v>
       </c>
       <c r="Q81">
-        <v>-10.995315424</v>
+        <v>-11.20572448</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1991367360873794</v>
+        <v>0.2068035728917484</v>
       </c>
       <c r="T81">
-        <v>3.541264112872504</v>
+        <v>3.718327318516129</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01359257084447925</v>
+        <v>0.01342266370892326</v>
       </c>
       <c r="W81">
-        <v>0.2325948717948718</v>
+        <v>0.2326349358974359</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.06178441292945114</v>
+        <v>0.06101210776783295</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2274686632962984</v>
+        <v>0.2293686632962984</v>
       </c>
       <c r="C82">
-        <v>-67.67365463776895</v>
+        <v>-69.00123202828384</v>
       </c>
       <c r="D82">
-        <v>17.73634536223107</v>
+        <v>17.55276797171618</v>
       </c>
       <c r="E82">
-        <v>50.92000000000001</v>
+        <v>52.06400000000001</v>
       </c>
       <c r="F82">
-        <v>91.52000000000001</v>
+        <v>92.66400000000002</v>
       </c>
       <c r="G82">
         <v>6.11</v>
@@ -7999,37 +7999,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M82">
-        <v>21.580416</v>
+        <v>21.85017120000001</v>
       </c>
       <c r="N82">
-        <v>-20.26374933333334</v>
+        <v>-20.53350453333334</v>
       </c>
       <c r="O82">
-        <v>-4.458024853333334</v>
+        <v>-4.517370997333335</v>
       </c>
       <c r="P82">
-        <v>-15.80572448</v>
+        <v>-16.01613353600001</v>
       </c>
       <c r="Q82">
-        <v>-11.20572448</v>
+        <v>-11.41613353600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2068035728917484</v>
+        <v>0.2152774451492089</v>
       </c>
       <c r="T82">
-        <v>3.718327318516129</v>
+        <v>3.914028756332768</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01342266370892326</v>
+        <v>0.01325695181128223</v>
       </c>
       <c r="W82">
-        <v>0.2326349358974359</v>
+        <v>0.2326740107628996</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.06101210776783295</v>
+        <v>0.06025887186946466</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2293686632962984</v>
+        <v>0.2312686632962984</v>
       </c>
       <c r="C83">
-        <v>-69.00123202828384</v>
+        <v>-70.32504816839899</v>
       </c>
       <c r="D83">
-        <v>17.55276797171618</v>
+        <v>17.37295183160101</v>
       </c>
       <c r="E83">
-        <v>52.06400000000001</v>
+        <v>53.20800000000001</v>
       </c>
       <c r="F83">
-        <v>92.66400000000002</v>
+        <v>93.80800000000001</v>
       </c>
       <c r="G83">
         <v>6.11</v>
@@ -8081,37 +8081,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M83">
-        <v>21.85017120000001</v>
+        <v>22.1199264</v>
       </c>
       <c r="N83">
-        <v>-20.53350453333334</v>
+        <v>-20.80325973333334</v>
       </c>
       <c r="O83">
-        <v>-4.517370997333335</v>
+        <v>-4.576717141333335</v>
       </c>
       <c r="P83">
-        <v>-16.01613353600001</v>
+        <v>-16.226542592</v>
       </c>
       <c r="Q83">
-        <v>-11.41613353600001</v>
+        <v>-11.626542592</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2152774451492089</v>
+        <v>0.2246928587686094</v>
       </c>
       <c r="T83">
-        <v>3.914028756332768</v>
+        <v>4.131474798351256</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01325695181128223</v>
+        <v>0.0130952816672422</v>
       </c>
       <c r="W83">
-        <v>0.2326740107628996</v>
+        <v>0.2327121325828643</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06025887186946466</v>
+        <v>0.05952400757837362</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2312686632962984</v>
+        <v>0.2331686632962984</v>
       </c>
       <c r="C84">
-        <v>-70.32504816839899</v>
+        <v>-71.64521748027502</v>
       </c>
       <c r="D84">
-        <v>17.37295183160101</v>
+        <v>17.19678251972499</v>
       </c>
       <c r="E84">
-        <v>53.20800000000001</v>
+        <v>54.35200000000001</v>
       </c>
       <c r="F84">
-        <v>93.80800000000001</v>
+        <v>94.95200000000001</v>
       </c>
       <c r="G84">
         <v>6.11</v>
@@ -8163,37 +8163,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M84">
-        <v>22.1199264</v>
+        <v>22.3896816</v>
       </c>
       <c r="N84">
-        <v>-20.80325973333334</v>
+        <v>-21.07301493333334</v>
       </c>
       <c r="O84">
-        <v>-4.576717141333335</v>
+        <v>-4.636063285333334</v>
       </c>
       <c r="P84">
-        <v>-16.226542592</v>
+        <v>-16.436951648</v>
       </c>
       <c r="Q84">
-        <v>-11.626542592</v>
+        <v>-11.836951648</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2246928587686094</v>
+        <v>0.2352159681079394</v>
       </c>
       <c r="T84">
-        <v>4.131474798351256</v>
+        <v>4.374502727666036</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0130952816672422</v>
+        <v>0.01293750718932362</v>
       </c>
       <c r="W84">
-        <v>0.2327121325828643</v>
+        <v>0.2327493358047575</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.05952400757837362</v>
+        <v>0.05880685086056192</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2331686632962984</v>
+        <v>0.2350686632962984</v>
       </c>
       <c r="C85">
-        <v>-71.64521748027502</v>
+        <v>-72.96184979150092</v>
       </c>
       <c r="D85">
-        <v>17.19678251972499</v>
+        <v>17.02415020849909</v>
       </c>
       <c r="E85">
-        <v>54.35200000000001</v>
+        <v>55.49600000000002</v>
       </c>
       <c r="F85">
-        <v>94.95200000000001</v>
+        <v>96.09600000000002</v>
       </c>
       <c r="G85">
         <v>6.11</v>
@@ -8245,37 +8245,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M85">
-        <v>22.3896816</v>
+        <v>22.65943680000001</v>
       </c>
       <c r="N85">
-        <v>-21.07301493333334</v>
+        <v>-21.34277013333334</v>
       </c>
       <c r="O85">
-        <v>-4.636063285333334</v>
+        <v>-4.695409429333335</v>
       </c>
       <c r="P85">
-        <v>-16.436951648</v>
+        <v>-16.647360704</v>
       </c>
       <c r="Q85">
-        <v>-11.836951648</v>
+        <v>-12.047360704</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2352159681079394</v>
+        <v>0.2470544661146856</v>
       </c>
       <c r="T85">
-        <v>4.374502727666036</v>
+        <v>4.647909148145164</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01293750718932362</v>
+        <v>0.01278348924659358</v>
       </c>
       <c r="W85">
-        <v>0.2327493358047575</v>
+        <v>0.2327856532356533</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05880685086056192</v>
+        <v>0.05810676930269798</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2350686632962984</v>
+        <v>0.2369686632962984</v>
       </c>
       <c r="C86">
-        <v>-72.96184979150094</v>
+        <v>-74.27505056341832</v>
       </c>
       <c r="D86">
-        <v>17.02415020849907</v>
+        <v>16.85494943658169</v>
       </c>
       <c r="E86">
-        <v>55.496</v>
+        <v>56.64000000000001</v>
       </c>
       <c r="F86">
-        <v>96.096</v>
+        <v>97.24000000000001</v>
       </c>
       <c r="G86">
         <v>6.11</v>
@@ -8327,37 +8327,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M86">
-        <v>22.6594368</v>
+        <v>22.929192</v>
       </c>
       <c r="N86">
-        <v>-21.34277013333334</v>
+        <v>-21.61252533333334</v>
       </c>
       <c r="O86">
-        <v>-4.695409429333334</v>
+        <v>-4.754755573333334</v>
       </c>
       <c r="P86">
-        <v>-16.647360704</v>
+        <v>-16.85776976</v>
       </c>
       <c r="Q86">
-        <v>-12.047360704</v>
+        <v>-12.25776976</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2470544661146855</v>
+        <v>0.2604714305223311</v>
       </c>
       <c r="T86">
-        <v>4.64790914814516</v>
+        <v>4.957769758021505</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01278348924659358</v>
+        <v>0.01263309525545718</v>
       </c>
       <c r="W86">
-        <v>0.2327856532356533</v>
+        <v>0.2328211161387632</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.05810676930269809</v>
+        <v>0.05742316025207805</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2369686632962984</v>
+        <v>0.2388686632962984</v>
       </c>
       <c r="C87">
-        <v>-74.27505056341832</v>
+        <v>-75.58492110596387</v>
       </c>
       <c r="D87">
-        <v>16.85494943658169</v>
+        <v>16.68907889403613</v>
       </c>
       <c r="E87">
-        <v>56.64000000000001</v>
+        <v>57.784</v>
       </c>
       <c r="F87">
-        <v>97.24000000000001</v>
+        <v>98.384</v>
       </c>
       <c r="G87">
         <v>6.11</v>
@@ -8409,37 +8409,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M87">
-        <v>22.929192</v>
+        <v>23.1989472</v>
       </c>
       <c r="N87">
-        <v>-21.61252533333334</v>
+        <v>-21.88228053333334</v>
       </c>
       <c r="O87">
-        <v>-4.754755573333334</v>
+        <v>-4.814101717333334</v>
       </c>
       <c r="P87">
-        <v>-16.85776976</v>
+        <v>-17.068178816</v>
       </c>
       <c r="Q87">
-        <v>-12.25776976</v>
+        <v>-12.468178816</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2604714305223311</v>
+        <v>0.2758051041310691</v>
       </c>
       <c r="T87">
-        <v>4.957769758021505</v>
+        <v>5.311896169308755</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01263309525545718</v>
+        <v>0.01248619879899838</v>
       </c>
       <c r="W87">
-        <v>0.2328211161387632</v>
+        <v>0.2328557543231962</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.05742316025207805</v>
+        <v>0.05675544908635621</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2388686632962984</v>
+        <v>0.2407686632962984</v>
       </c>
       <c r="C88">
-        <v>-75.58492110596387</v>
+        <v>-76.89155877994986</v>
       </c>
       <c r="D88">
-        <v>16.68907889403613</v>
+        <v>16.52644122005014</v>
       </c>
       <c r="E88">
-        <v>57.784</v>
+        <v>58.928</v>
       </c>
       <c r="F88">
-        <v>98.384</v>
+        <v>99.52800000000001</v>
       </c>
       <c r="G88">
         <v>6.11</v>
@@ -8491,37 +8491,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M88">
-        <v>23.1989472</v>
+        <v>23.4687024</v>
       </c>
       <c r="N88">
-        <v>-21.88228053333334</v>
+        <v>-22.15203573333334</v>
       </c>
       <c r="O88">
-        <v>-4.814101717333334</v>
+        <v>-4.873447861333334</v>
       </c>
       <c r="P88">
-        <v>-17.068178816</v>
+        <v>-17.278587872</v>
       </c>
       <c r="Q88">
-        <v>-12.468178816</v>
+        <v>-12.678587872</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2758051041310691</v>
+        <v>0.2934978044488437</v>
       </c>
       <c r="T88">
-        <v>5.311896169308755</v>
+        <v>5.72050356694789</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01248619879899838</v>
+        <v>0.01234267927257311</v>
       </c>
       <c r="W88">
-        <v>0.2328557543231962</v>
+        <v>0.2328895962275273</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.05675544908635621</v>
+        <v>0.05610308760260496</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2407686632962984</v>
+        <v>0.2426686632962984</v>
       </c>
       <c r="C89">
-        <v>-76.89155877994986</v>
+        <v>-78.19505718763114</v>
       </c>
       <c r="D89">
-        <v>16.52644122005014</v>
+        <v>16.36694281236887</v>
       </c>
       <c r="E89">
-        <v>58.928</v>
+        <v>60.07200000000001</v>
       </c>
       <c r="F89">
-        <v>99.52800000000001</v>
+        <v>100.672</v>
       </c>
       <c r="G89">
         <v>6.11</v>
@@ -8573,37 +8573,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M89">
-        <v>23.4687024</v>
+        <v>23.7384576</v>
       </c>
       <c r="N89">
-        <v>-22.15203573333334</v>
+        <v>-22.42179093333334</v>
       </c>
       <c r="O89">
-        <v>-4.873447861333334</v>
+        <v>-4.932794005333334</v>
       </c>
       <c r="P89">
-        <v>-17.278587872</v>
+        <v>-17.488996928</v>
       </c>
       <c r="Q89">
-        <v>-12.678587872</v>
+        <v>-12.888996928</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2934978044488437</v>
+        <v>0.314139288152914</v>
       </c>
       <c r="T89">
-        <v>5.72050356694789</v>
+        <v>6.197212197526883</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01234267927257311</v>
+        <v>0.0122024215535666</v>
       </c>
       <c r="W89">
-        <v>0.2328895962275273</v>
+        <v>0.232922668997669</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05610308760260496</v>
+        <v>0.05546555251621177</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2426686632962984</v>
+        <v>0.2445686632962984</v>
       </c>
       <c r="C90">
-        <v>-78.19505718763114</v>
+        <v>-79.49550635234249</v>
       </c>
       <c r="D90">
-        <v>16.36694281236887</v>
+        <v>16.21049364765751</v>
       </c>
       <c r="E90">
-        <v>60.07200000000001</v>
+        <v>61.216</v>
       </c>
       <c r="F90">
-        <v>100.672</v>
+        <v>101.816</v>
       </c>
       <c r="G90">
         <v>6.11</v>
@@ -8655,37 +8655,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M90">
-        <v>23.7384576</v>
+        <v>24.0082128</v>
       </c>
       <c r="N90">
-        <v>-22.42179093333334</v>
+        <v>-22.69154613333334</v>
       </c>
       <c r="O90">
-        <v>-4.932794005333334</v>
+        <v>-4.992140149333334</v>
       </c>
       <c r="P90">
-        <v>-17.488996928</v>
+        <v>-17.699405984</v>
       </c>
       <c r="Q90">
-        <v>-12.888996928</v>
+        <v>-13.099405984</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.314139288152914</v>
+        <v>0.338533768894088</v>
       </c>
       <c r="T90">
-        <v>6.197212197526883</v>
+        <v>6.76059512457478</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0122024215535666</v>
+        <v>0.01206531569341416</v>
       </c>
       <c r="W90">
-        <v>0.232922668997669</v>
+        <v>0.2329549985594929</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.05546555251621177</v>
+        <v>0.05484234406097344</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2445686632962984</v>
+        <v>0.2464686632962984</v>
       </c>
       <c r="C91">
-        <v>-79.49550635234249</v>
+        <v>-80.79299288793112</v>
       </c>
       <c r="D91">
-        <v>16.21049364765751</v>
+        <v>16.05700711206888</v>
       </c>
       <c r="E91">
-        <v>61.216</v>
+        <v>62.36000000000001</v>
       </c>
       <c r="F91">
-        <v>101.816</v>
+        <v>102.96</v>
       </c>
       <c r="G91">
         <v>6.11</v>
@@ -8737,37 +8737,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M91">
-        <v>24.0082128</v>
+        <v>24.277968</v>
       </c>
       <c r="N91">
-        <v>-22.69154613333334</v>
+        <v>-22.96130133333333</v>
       </c>
       <c r="O91">
-        <v>-4.992140149333334</v>
+        <v>-5.051486293333333</v>
       </c>
       <c r="P91">
-        <v>-17.699405984</v>
+        <v>-17.90981504</v>
       </c>
       <c r="Q91">
-        <v>-13.099405984</v>
+        <v>-13.30981504</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.338533768894088</v>
+        <v>0.3678071457834968</v>
       </c>
       <c r="T91">
-        <v>6.76059512457478</v>
+        <v>7.43665463703226</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01206531569341416</v>
+        <v>0.011931256630154</v>
       </c>
       <c r="W91">
-        <v>0.2329549985594929</v>
+        <v>0.2329866096866097</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05484234406097344</v>
+        <v>0.05423298468251814</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2464686632962984</v>
+        <v>0.2483686632962984</v>
       </c>
       <c r="C92">
-        <v>-80.79299288793112</v>
+        <v>-82.08760015865349</v>
       </c>
       <c r="D92">
-        <v>16.05700711206888</v>
+        <v>15.90639984134653</v>
       </c>
       <c r="E92">
-        <v>62.36000000000001</v>
+        <v>63.50400000000001</v>
       </c>
       <c r="F92">
-        <v>102.96</v>
+        <v>104.104</v>
       </c>
       <c r="G92">
         <v>6.11</v>
@@ -8819,37 +8819,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M92">
-        <v>24.277968</v>
+        <v>24.5477232</v>
       </c>
       <c r="N92">
-        <v>-22.96130133333333</v>
+        <v>-23.23105653333334</v>
       </c>
       <c r="O92">
-        <v>-5.051486293333333</v>
+        <v>-5.110832437333334</v>
       </c>
       <c r="P92">
-        <v>-17.90981504</v>
+        <v>-18.120224096</v>
       </c>
       <c r="Q92">
-        <v>-13.30981504</v>
+        <v>-13.520224096</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3678071457834968</v>
+        <v>0.4035857175372188</v>
       </c>
       <c r="T92">
-        <v>7.43665463703226</v>
+        <v>8.262949596702512</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.011931256630154</v>
+        <v>0.01180014391993253</v>
       </c>
       <c r="W92">
-        <v>0.2329866096866097</v>
+        <v>0.2330175260636799</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.05423298468251814</v>
+        <v>0.05363701781787511</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2483686632962984</v>
+        <v>0.2502686632962984</v>
       </c>
       <c r="C93">
-        <v>-82.08760015865349</v>
+        <v>-83.37940843015747</v>
       </c>
       <c r="D93">
-        <v>15.90639984134653</v>
+        <v>15.75859156984254</v>
       </c>
       <c r="E93">
-        <v>63.50400000000001</v>
+        <v>64.648</v>
       </c>
       <c r="F93">
-        <v>104.104</v>
+        <v>105.248</v>
       </c>
       <c r="G93">
         <v>6.11</v>
@@ -8901,37 +8901,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M93">
-        <v>24.5477232</v>
+        <v>24.8174784</v>
       </c>
       <c r="N93">
-        <v>-23.23105653333334</v>
+        <v>-23.50081173333334</v>
       </c>
       <c r="O93">
-        <v>-5.110832437333334</v>
+        <v>-5.170178581333334</v>
       </c>
       <c r="P93">
-        <v>-18.120224096</v>
+        <v>-18.330633152</v>
       </c>
       <c r="Q93">
-        <v>-13.520224096</v>
+        <v>-13.730633152</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4035857175372188</v>
+        <v>0.4483089322293712</v>
       </c>
       <c r="T93">
-        <v>8.262949596702512</v>
+        <v>9.295818296290328</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01180014391993253</v>
+        <v>0.01167188148602022</v>
       </c>
       <c r="W93">
-        <v>0.2330175260636799</v>
+        <v>0.2330477703455964</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05363701781787511</v>
+        <v>0.05305400675463734</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2502686632962984</v>
+        <v>0.2521686632962984</v>
       </c>
       <c r="C94">
-        <v>-83.37940843015747</v>
+        <v>-84.6684950121242</v>
       </c>
       <c r="D94">
-        <v>15.75859156984254</v>
+        <v>15.61350498787581</v>
       </c>
       <c r="E94">
-        <v>64.648</v>
+        <v>65.792</v>
       </c>
       <c r="F94">
-        <v>105.248</v>
+        <v>106.392</v>
       </c>
       <c r="G94">
         <v>6.11</v>
@@ -8983,37 +8983,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M94">
-        <v>24.8174784</v>
+        <v>25.0872336</v>
       </c>
       <c r="N94">
-        <v>-23.50081173333334</v>
+        <v>-23.77056693333334</v>
       </c>
       <c r="O94">
-        <v>-5.170178581333334</v>
+        <v>-5.229524725333334</v>
       </c>
       <c r="P94">
-        <v>-18.330633152</v>
+        <v>-18.541042208</v>
       </c>
       <c r="Q94">
-        <v>-13.730633152</v>
+        <v>-13.941042208</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4483089322293712</v>
+        <v>0.5058102082621385</v>
       </c>
       <c r="T94">
-        <v>9.295818296290328</v>
+        <v>10.62379233861752</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01167188148602022</v>
+        <v>0.01154637738402001</v>
       </c>
       <c r="W94">
-        <v>0.2330477703455964</v>
+        <v>0.2330773642128481</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05305400675463734</v>
+        <v>0.05248353356372726</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2521686632962984</v>
+        <v>0.2540686632962984</v>
       </c>
       <c r="C95">
-        <v>-84.6684950121242</v>
+        <v>-85.95493439310184</v>
       </c>
       <c r="D95">
-        <v>15.61350498787581</v>
+        <v>15.47106560689818</v>
       </c>
       <c r="E95">
-        <v>65.792</v>
+        <v>66.93600000000001</v>
       </c>
       <c r="F95">
-        <v>106.392</v>
+        <v>107.536</v>
       </c>
       <c r="G95">
         <v>6.11</v>
@@ -9065,37 +9065,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M95">
-        <v>25.0872336</v>
+        <v>25.3569888</v>
       </c>
       <c r="N95">
-        <v>-23.77056693333334</v>
+        <v>-24.04032213333334</v>
       </c>
       <c r="O95">
-        <v>-5.229524725333334</v>
+        <v>-5.288870869333334</v>
       </c>
       <c r="P95">
-        <v>-18.541042208</v>
+        <v>-18.751451264</v>
       </c>
       <c r="Q95">
-        <v>-13.941042208</v>
+        <v>-14.151451264</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5058102082621385</v>
+        <v>0.5824785763058284</v>
       </c>
       <c r="T95">
-        <v>10.62379233861752</v>
+        <v>12.39442439505378</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01154637738402001</v>
+        <v>0.01142354358206234</v>
       </c>
       <c r="W95">
-        <v>0.2330773642128481</v>
+        <v>0.2331063284233497</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05248353356372726</v>
+        <v>0.0519251981002834</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2540686632962984</v>
+        <v>0.2559686632962984</v>
       </c>
       <c r="C96">
-        <v>-85.95493439310184</v>
+        <v>-87.23879836802594</v>
       </c>
       <c r="D96">
-        <v>15.47106560689818</v>
+        <v>15.33120163197407</v>
       </c>
       <c r="E96">
-        <v>66.93600000000001</v>
+        <v>68.08000000000001</v>
       </c>
       <c r="F96">
-        <v>107.536</v>
+        <v>108.68</v>
       </c>
       <c r="G96">
         <v>6.11</v>
@@ -9147,37 +9147,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M96">
-        <v>25.3569888</v>
+        <v>25.626744</v>
       </c>
       <c r="N96">
-        <v>-24.04032213333334</v>
+        <v>-24.31007733333334</v>
       </c>
       <c r="O96">
-        <v>-5.288870869333334</v>
+        <v>-5.348217013333334</v>
       </c>
       <c r="P96">
-        <v>-18.751451264</v>
+        <v>-18.96186032</v>
       </c>
       <c r="Q96">
-        <v>-14.151451264</v>
+        <v>-14.36186032</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5824785763058284</v>
+        <v>0.6898142915669945</v>
       </c>
       <c r="T96">
-        <v>12.39442439505378</v>
+        <v>14.87330927406454</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01142354358206234</v>
+        <v>0.01130329575488274</v>
       </c>
       <c r="W96">
-        <v>0.2331063284233497</v>
+        <v>0.2331346828609986</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0519251981002834</v>
+        <v>0.05137861706764879</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2559686632962984</v>
+        <v>0.2578686632962984</v>
       </c>
       <c r="C97">
-        <v>-87.23879836802594</v>
+        <v>-88.5201561588847</v>
       </c>
       <c r="D97">
-        <v>15.33120163197407</v>
+        <v>15.1938438411153</v>
       </c>
       <c r="E97">
-        <v>68.08000000000001</v>
+        <v>69.22400000000002</v>
       </c>
       <c r="F97">
-        <v>108.68</v>
+        <v>109.824</v>
       </c>
       <c r="G97">
         <v>6.11</v>
@@ -9229,37 +9229,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M97">
-        <v>25.626744</v>
+        <v>25.8964992</v>
       </c>
       <c r="N97">
-        <v>-24.31007733333334</v>
+        <v>-24.57983253333334</v>
       </c>
       <c r="O97">
-        <v>-5.348217013333334</v>
+        <v>-5.407563157333334</v>
       </c>
       <c r="P97">
-        <v>-18.96186032</v>
+        <v>-19.172269376</v>
       </c>
       <c r="Q97">
-        <v>-14.36186032</v>
+        <v>-14.572269376</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6898142915669945</v>
+        <v>0.8508178644587434</v>
       </c>
       <c r="T97">
-        <v>14.87330927406454</v>
+        <v>18.59163659258068</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01130329575488274</v>
+        <v>0.01118555309076938</v>
       </c>
       <c r="W97">
-        <v>0.2331346828609986</v>
+        <v>0.2331624465811966</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05137861706764879</v>
+        <v>0.05084342313986079</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2578686632962984</v>
+        <v>0.2597686632962984</v>
       </c>
       <c r="C98">
-        <v>-88.52015615888469</v>
+        <v>-89.79907452895529</v>
       </c>
       <c r="D98">
-        <v>15.1938438411153</v>
+        <v>15.05892547104471</v>
       </c>
       <c r="E98">
-        <v>69.22399999999999</v>
+        <v>70.36799999999999</v>
       </c>
       <c r="F98">
-        <v>109.824</v>
+        <v>110.968</v>
       </c>
       <c r="G98">
         <v>6.11</v>
@@ -9311,37 +9311,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M98">
-        <v>25.8964992</v>
+        <v>26.1662544</v>
       </c>
       <c r="N98">
-        <v>-24.57983253333333</v>
+        <v>-24.84958773333334</v>
       </c>
       <c r="O98">
-        <v>-5.407563157333334</v>
+        <v>-5.466909301333335</v>
       </c>
       <c r="P98">
-        <v>-19.172269376</v>
+        <v>-19.382678432</v>
       </c>
       <c r="Q98">
-        <v>-14.572269376</v>
+        <v>-14.782678432</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8508178644587411</v>
+        <v>1.119157152611655</v>
       </c>
       <c r="T98">
-        <v>18.59163659258063</v>
+        <v>24.78884879010751</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01118555309076938</v>
+        <v>0.01107023811045217</v>
       </c>
       <c r="W98">
-        <v>0.2331624465811966</v>
+        <v>0.2331896378535554</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05084342313986079</v>
+        <v>0.05031926413841892</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2597686632962984</v>
+        <v>0.2616686632962984</v>
       </c>
       <c r="C99">
-        <v>-89.79907452895529</v>
+        <v>-91.0756178910074</v>
       </c>
       <c r="D99">
-        <v>15.05892547104471</v>
+        <v>14.92638210899262</v>
       </c>
       <c r="E99">
-        <v>70.36799999999999</v>
+        <v>71.512</v>
       </c>
       <c r="F99">
-        <v>110.968</v>
+        <v>112.112</v>
       </c>
       <c r="G99">
         <v>6.11</v>
@@ -9393,37 +9393,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M99">
-        <v>26.1662544</v>
+        <v>26.4360096</v>
       </c>
       <c r="N99">
-        <v>-24.84958773333334</v>
+        <v>-25.11934293333334</v>
       </c>
       <c r="O99">
-        <v>-5.466909301333335</v>
+        <v>-5.526255445333334</v>
       </c>
       <c r="P99">
-        <v>-19.382678432</v>
+        <v>-19.593087488</v>
       </c>
       <c r="Q99">
-        <v>-14.782678432</v>
+        <v>-14.993087488</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.119157152611655</v>
+        <v>1.655835728917482</v>
       </c>
       <c r="T99">
-        <v>24.78884879010751</v>
+        <v>37.18327318516126</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01107023811045217</v>
+        <v>0.01095727649708021</v>
       </c>
       <c r="W99">
-        <v>0.2331896378535554</v>
+        <v>0.2332162742019885</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05031926413841892</v>
+        <v>0.04980580225945541</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2616686632962984</v>
+        <v>0.2635686632962984</v>
       </c>
       <c r="C100">
-        <v>-91.0756178910074</v>
+        <v>-92.34984840984241</v>
       </c>
       <c r="D100">
-        <v>14.92638210899262</v>
+        <v>14.7961515901576</v>
       </c>
       <c r="E100">
-        <v>71.512</v>
+        <v>72.65600000000001</v>
       </c>
       <c r="F100">
-        <v>112.112</v>
+        <v>113.256</v>
       </c>
       <c r="G100">
         <v>6.11</v>
@@ -9475,37 +9475,37 @@
         <v>1.316666666666667</v>
       </c>
       <c r="M100">
-        <v>26.4360096</v>
+        <v>26.7057648</v>
       </c>
       <c r="N100">
-        <v>-25.11934293333334</v>
+        <v>-25.38909813333333</v>
       </c>
       <c r="O100">
-        <v>-5.526255445333334</v>
+        <v>-5.585601589333334</v>
       </c>
       <c r="P100">
-        <v>-19.593087488</v>
+        <v>-19.803496544</v>
       </c>
       <c r="Q100">
-        <v>-14.993087488</v>
+        <v>-15.203496544</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.655835728917482</v>
+        <v>3.265871457834964</v>
       </c>
       <c r="T100">
-        <v>37.18327318516126</v>
+        <v>74.36654637032251</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01095727649708021</v>
+        <v>0.01084659693650364</v>
       </c>
       <c r="W100">
-        <v>0.2332162742019885</v>
+        <v>0.2332423724423724</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04980580225945541</v>
+        <v>0.04930271334774383</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2635686632962984</v>
-      </c>
-      <c r="C101">
-        <v>-92.34984840984241</v>
-      </c>
-      <c r="D101">
-        <v>14.7961515901576</v>
-      </c>
-      <c r="E101">
-        <v>72.65600000000001</v>
-      </c>
-      <c r="F101">
-        <v>113.256</v>
-      </c>
-      <c r="G101">
-        <v>6.11</v>
-      </c>
-      <c r="H101">
-        <v>73.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="K101">
-        <v>4.6</v>
-      </c>
-      <c r="L101">
-        <v>1.316666666666667</v>
-      </c>
-      <c r="M101">
-        <v>26.7057648</v>
-      </c>
-      <c r="N101">
-        <v>-25.38909813333333</v>
-      </c>
-      <c r="O101">
-        <v>-5.585601589333334</v>
-      </c>
-      <c r="P101">
-        <v>-19.803496544</v>
-      </c>
-      <c r="Q101">
-        <v>-15.203496544</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.265871457834964</v>
-      </c>
-      <c r="T101">
-        <v>74.36654637032251</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01084659693650364</v>
-      </c>
-      <c r="W101">
-        <v>0.2332423724423724</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04930271334774383</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
